--- a/investment-engine/sector/AI/stock-data/investment_data_06182026.xlsx
+++ b/investment-engine/sector/AI/stock-data/investment_data_06182026.xlsx
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>204.65</v>
+        <v>206.96</v>
       </c>
       <c r="D2" t="n">
-        <v>45.34</v>
+        <v>47.38</v>
       </c>
       <c r="E2" t="n">
-        <v>31.34</v>
+        <v>31.69</v>
       </c>
       <c r="F2" t="n">
-        <v>19.54</v>
+        <v>19.76</v>
       </c>
       <c r="G2" t="n">
-        <v>4952529850000</v>
+        <v>5008311040000</v>
       </c>
       <c r="H2" t="n">
-        <v>163.72</v>
+        <v>165.57</v>
       </c>
       <c r="I2" t="n">
         <v>309.93</v>
@@ -579,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>51.44</v>
+        <v>49.75</v>
       </c>
       <c r="L2" t="n">
         <v>85.23</v>
@@ -597,19 +597,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
         <v>4.09</v>
       </c>
       <c r="S2" t="n">
-        <v>69.2</v>
+        <v>69.19</v>
       </c>
       <c r="T2" t="n">
         <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>74.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.78</v>
+        <v>28.53</v>
       </c>
       <c r="D3" t="n">
-        <v>38.04</v>
+        <v>39.52</v>
       </c>
       <c r="E3" t="n">
-        <v>14.65</v>
+        <v>15.05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="G3" t="n">
-        <v>17970130000</v>
+        <v>18455280000</v>
       </c>
       <c r="H3" t="n">
-        <v>22.22</v>
+        <v>22.82</v>
       </c>
       <c r="I3" t="n">
         <v>35.87</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>29.12</v>
+        <v>25.73</v>
       </c>
       <c r="L3" t="n">
         <v>122.68</v>
@@ -666,7 +666,7 @@
         <v>1.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R3" t="n">
         <v>13.87</v>
@@ -678,7 +678,7 @@
         <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>66.90000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="4">
@@ -693,22 +693,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>378.91</v>
+        <v>377.5</v>
       </c>
       <c r="D4" t="n">
-        <v>34.59</v>
+        <v>34.11</v>
       </c>
       <c r="E4" t="n">
-        <v>22.57</v>
+        <v>22.48</v>
       </c>
       <c r="F4" t="n">
-        <v>8.84</v>
+        <v>8.81</v>
       </c>
       <c r="G4" t="n">
-        <v>2814708170000</v>
+        <v>2804234050000</v>
       </c>
       <c r="H4" t="n">
-        <v>303.13</v>
+        <v>302</v>
       </c>
       <c r="I4" t="n">
         <v>559.29</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>47.6</v>
+        <v>48.16</v>
       </c>
       <c r="L4" t="n">
         <v>18.3</v>
@@ -735,19 +735,19 @@
         <v>0.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="R4" t="n">
         <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>74.77</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>1.23</v>
       </c>
       <c r="U4" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="5">
@@ -762,31 +762,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1043.19</v>
+        <v>1089.13</v>
       </c>
       <c r="D5" t="n">
-        <v>61.74</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>49.25</v>
+        <v>51.42</v>
       </c>
       <c r="F5" t="n">
-        <v>20.24</v>
+        <v>21.13</v>
       </c>
       <c r="G5" t="n">
-        <v>1176440780000</v>
+        <v>1228248940000</v>
       </c>
       <c r="H5" t="n">
-        <v>834.55</v>
+        <v>871.3</v>
       </c>
       <c r="I5" t="n">
-        <v>963.52</v>
+        <v>1002.27</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-7.64</v>
+        <v>-7.98</v>
       </c>
       <c r="L5" t="n">
         <v>196.29</v>
@@ -804,7 +804,7 @@
         <v>0.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
         <v>0.44</v>
@@ -816,145 +816,145 @@
         <v>1.35</v>
       </c>
       <c r="U5" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLAB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31.01</v>
+        <v>362.7</v>
       </c>
       <c r="D6" t="n">
-        <v>36.56</v>
+        <v>45.41</v>
       </c>
       <c r="E6" t="n">
-        <v>11.36</v>
+        <v>27.67</v>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>10.36</v>
       </c>
       <c r="G6" t="n">
-        <v>1828470000</v>
+        <v>4385321639999</v>
       </c>
       <c r="H6" t="n">
-        <v>24.81</v>
+        <v>290.16</v>
       </c>
       <c r="I6" t="n">
-        <v>43</v>
+        <v>433.97</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>38.66</v>
+        <v>19.65</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5</v>
+        <v>22.34</v>
       </c>
       <c r="M6" t="n">
-        <v>268.2</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>33.77</v>
+        <v>60.43</v>
       </c>
       <c r="O6" t="n">
-        <v>18.47</v>
+        <v>37.86</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R6" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>38.87</v>
+      </c>
+      <c r="T6" t="n">
         <v>1.38</v>
       </c>
-      <c r="R6" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="S6" t="n">
-        <v>95.68000000000001</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
       <c r="U6" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PLAB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>363.79</v>
+        <v>32.11</v>
       </c>
       <c r="D7" t="n">
-        <v>46.1</v>
+        <v>39.43</v>
       </c>
       <c r="E7" t="n">
-        <v>27.75</v>
+        <v>11.76</v>
       </c>
       <c r="F7" t="n">
-        <v>10.39</v>
+        <v>2.2</v>
       </c>
       <c r="G7" t="n">
-        <v>4396287980000</v>
+        <v>1893320000</v>
       </c>
       <c r="H7" t="n">
-        <v>291.03</v>
+        <v>25.69</v>
       </c>
       <c r="I7" t="n">
-        <v>433.97</v>
+        <v>43</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>19.29</v>
+        <v>33.91</v>
       </c>
       <c r="L7" t="n">
-        <v>22.34</v>
+        <v>-0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>81.95999999999999</v>
+        <v>268.2</v>
       </c>
       <c r="N7" t="n">
-        <v>60.43</v>
+        <v>33.77</v>
       </c>
       <c r="O7" t="n">
-        <v>37.86</v>
+        <v>18.47</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="R7" t="n">
-        <v>52.1</v>
+        <v>4.06</v>
       </c>
       <c r="S7" t="n">
-        <v>38.87</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8">
@@ -969,22 +969,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>249.33</v>
+        <v>259.5</v>
       </c>
       <c r="D8" t="n">
-        <v>60.25</v>
+        <v>62.85</v>
       </c>
       <c r="E8" t="n">
-        <v>100.54</v>
+        <v>104.65</v>
       </c>
       <c r="F8" t="n">
-        <v>34.82</v>
+        <v>36.24</v>
       </c>
       <c r="G8" t="n">
-        <v>46494530000</v>
+        <v>48390990000</v>
       </c>
       <c r="H8" t="n">
-        <v>199.46</v>
+        <v>207.6</v>
       </c>
       <c r="I8" t="n">
         <v>266.44</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.86</v>
+        <v>2.67</v>
       </c>
       <c r="L8" t="n">
         <v>157.02</v>
@@ -1011,157 +1011,157 @@
         <v>0.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="R8" t="n">
         <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>75.22</v>
+        <v>75.39</v>
       </c>
       <c r="T8" t="n">
         <v>1.15</v>
       </c>
       <c r="U8" t="n">
-        <v>62.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STRL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>838.21</v>
+        <v>238.35</v>
       </c>
       <c r="D9" t="n">
-        <v>53.18</v>
+        <v>37.87</v>
       </c>
       <c r="E9" t="n">
-        <v>74.94</v>
+        <v>28.48</v>
       </c>
       <c r="F9" t="n">
-        <v>8.92</v>
+        <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>25721270000</v>
+        <v>2563957090000</v>
       </c>
       <c r="H9" t="n">
-        <v>670.5700000000001</v>
+        <v>190.68</v>
       </c>
       <c r="I9" t="n">
-        <v>956.4299999999999</v>
+        <v>316.56</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>14.1</v>
+        <v>32.81</v>
       </c>
       <c r="L9" t="n">
-        <v>91.59</v>
+        <v>16.61</v>
       </c>
       <c r="M9" t="n">
-        <v>141.86</v>
+        <v>75.33</v>
       </c>
       <c r="N9" t="n">
-        <v>22.43</v>
+        <v>50.6</v>
       </c>
       <c r="O9" t="n">
-        <v>12.02</v>
+        <v>12.22</v>
       </c>
       <c r="P9" t="n">
-        <v>0.29</v>
+        <v>0.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>2.43</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>93.26000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="U9" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>STRL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>237.5</v>
+        <v>856.5</v>
       </c>
       <c r="D10" t="n">
-        <v>36.89</v>
+        <v>54.94</v>
       </c>
       <c r="E10" t="n">
-        <v>28.38</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>3.44</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>2554813480000</v>
+        <v>26282520000</v>
       </c>
       <c r="H10" t="n">
-        <v>190</v>
+        <v>685.2</v>
       </c>
       <c r="I10" t="n">
-        <v>316.56</v>
+        <v>956.4299999999999</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>33.29</v>
+        <v>11.67</v>
       </c>
       <c r="L10" t="n">
-        <v>16.61</v>
+        <v>91.59</v>
       </c>
       <c r="M10" t="n">
-        <v>75.33</v>
+        <v>141.86</v>
       </c>
       <c r="N10" t="n">
-        <v>50.6</v>
+        <v>22.43</v>
       </c>
       <c r="O10" t="n">
-        <v>12.22</v>
+        <v>12.02</v>
       </c>
       <c r="P10" t="n">
-        <v>0.51</v>
+        <v>0.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>8.949999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="S10" t="n">
-        <v>66.63</v>
+        <v>93.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="n">
-        <v>61.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="11">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>392.9</v>
+        <v>403.89</v>
       </c>
       <c r="D11" t="n">
-        <v>46.15</v>
+        <v>49.36</v>
       </c>
       <c r="E11" t="n">
-        <v>65.41</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>24.77</v>
+        <v>25.46</v>
       </c>
       <c r="G11" t="n">
-        <v>1869253180000</v>
+        <v>1921539080000</v>
       </c>
       <c r="H11" t="n">
-        <v>314.32</v>
+        <v>323.11</v>
       </c>
       <c r="I11" t="n">
         <v>524.1799999999999</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>33.41</v>
+        <v>29.78</v>
       </c>
       <c r="L11" t="n">
         <v>47.87</v>
@@ -1224,208 +1224,208 @@
         <v>1.94</v>
       </c>
       <c r="S11" t="n">
-        <v>78.68000000000001</v>
+        <v>78.69</v>
       </c>
       <c r="T11" t="n">
         <v>1.33</v>
       </c>
       <c r="U11" t="n">
-        <v>60.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>419.32</v>
+        <v>333.11</v>
       </c>
       <c r="D12" t="n">
-        <v>67.58</v>
-      </c>
-      <c r="E12" t="n">
-        <v>33.32</v>
+        <v>49.77</v>
       </c>
       <c r="F12" t="n">
-        <v>2.03</v>
+        <v>10.3</v>
       </c>
       <c r="G12" t="n">
-        <v>271764640000</v>
+        <v>26792680000</v>
       </c>
       <c r="H12" t="n">
-        <v>335.46</v>
+        <v>266.49</v>
       </c>
       <c r="I12" t="n">
-        <v>496.76</v>
+        <v>399.82</v>
       </c>
       <c r="K12" t="n">
-        <v>18.47</v>
+        <v>20.03</v>
       </c>
       <c r="L12" t="n">
-        <v>87.48999999999999</v>
+        <v>25.25</v>
       </c>
       <c r="M12" t="n">
-        <v>281.26</v>
+        <v>111.72</v>
       </c>
       <c r="N12" t="n">
-        <v>19.09</v>
+        <v>71.67</v>
       </c>
       <c r="O12" t="n">
-        <v>6.27</v>
+        <v>-1.12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="R12" t="n">
-        <v>53.55</v>
+        <v>4.01</v>
       </c>
       <c r="S12" t="n">
-        <v>39.86</v>
+        <v>90.63</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="U12" t="n">
-        <v>59.4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>432.15</v>
+        <v>428</v>
       </c>
       <c r="D13" t="n">
-        <v>55.24</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>35.92</v>
+        <v>34.01</v>
       </c>
       <c r="F13" t="n">
-        <v>16.87</v>
+        <v>2.07</v>
       </c>
       <c r="G13" t="n">
-        <v>2241337300000</v>
+        <v>277390210000</v>
       </c>
       <c r="H13" t="n">
-        <v>345.72</v>
+        <v>342.4</v>
       </c>
       <c r="I13" t="n">
-        <v>460.4</v>
-      </c>
-      <c r="J13" t="b">
-        <v>0</v>
+        <v>499.86</v>
       </c>
       <c r="K13" t="n">
-        <v>6.54</v>
+        <v>16.79</v>
       </c>
       <c r="L13" t="n">
-        <v>40.49</v>
+        <v>87.48999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>64.59999999999999</v>
+        <v>281.26</v>
       </c>
       <c r="N13" t="n">
-        <v>60.72</v>
+        <v>19.09</v>
       </c>
       <c r="O13" t="n">
-        <v>46.96</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.19</v>
+        <v>6.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0.09</v>
+        <v>53.55</v>
       </c>
       <c r="S13" t="n">
-        <v>15.17</v>
+        <v>39.86</v>
       </c>
       <c r="T13" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>59.3</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>334.69</v>
+        <v>438.75</v>
       </c>
       <c r="D14" t="n">
-        <v>50.23</v>
+        <v>57.34</v>
+      </c>
+      <c r="E14" t="n">
+        <v>36.46</v>
       </c>
       <c r="F14" t="n">
-        <v>10.34</v>
+        <v>17.13</v>
       </c>
       <c r="G14" t="n">
-        <v>26919760000</v>
+        <v>2275557180000</v>
       </c>
       <c r="H14" t="n">
-        <v>267.75</v>
+        <v>351</v>
       </c>
       <c r="I14" t="n">
-        <v>399.82</v>
+        <v>460.4</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>19.46</v>
+        <v>4.93</v>
       </c>
       <c r="L14" t="n">
-        <v>25.25</v>
+        <v>40.49</v>
       </c>
       <c r="M14" t="n">
-        <v>111.72</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>71.67</v>
+        <v>60.72</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.12</v>
+        <v>46.96</v>
       </c>
       <c r="P14" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="R14" t="n">
-        <v>4.01</v>
+        <v>0.09</v>
       </c>
       <c r="S14" t="n">
-        <v>90.63</v>
+        <v>15.16</v>
       </c>
       <c r="T14" t="n">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="U14" t="n">
-        <v>58.8</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="15">
@@ -1440,22 +1440,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>267.17</v>
+        <v>269.96</v>
       </c>
       <c r="D15" t="n">
-        <v>47.79</v>
+        <v>49.44</v>
       </c>
       <c r="E15" t="n">
-        <v>23.2</v>
+        <v>23.44</v>
       </c>
       <c r="F15" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="G15" t="n">
-        <v>96499160000</v>
+        <v>97505450000</v>
       </c>
       <c r="H15" t="n">
-        <v>213.74</v>
+        <v>215.97</v>
       </c>
       <c r="I15" t="n">
         <v>365.11</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>36.66</v>
+        <v>35.25</v>
       </c>
       <c r="L15" t="n">
         <v>23.45</v>
@@ -1488,13 +1488,13 @@
         <v>6.48</v>
       </c>
       <c r="S15" t="n">
-        <v>73.70999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.35</v>
       </c>
       <c r="U15" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="16">
@@ -1509,22 +1509,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>869.98</v>
+        <v>885.98</v>
       </c>
       <c r="D16" t="n">
-        <v>47.35</v>
+        <v>48.76</v>
       </c>
       <c r="E16" t="n">
-        <v>161.46</v>
+        <v>164.43</v>
       </c>
       <c r="F16" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="G16" t="n">
-        <v>67684450000</v>
+        <v>68929370000</v>
       </c>
       <c r="H16" t="n">
-        <v>695.98</v>
+        <v>708.78</v>
       </c>
       <c r="I16" t="n">
         <v>1132.81</v>
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>30.21</v>
+        <v>27.86</v>
       </c>
       <c r="L16" t="n">
         <v>90.12</v>
@@ -1557,220 +1557,220 @@
         <v>2.57</v>
       </c>
       <c r="S16" t="n">
-        <v>102.92</v>
+        <v>102.9</v>
       </c>
       <c r="T16" t="n">
         <v>1.48</v>
       </c>
       <c r="U16" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Construction</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>NOW</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1931.77</v>
+        <v>94.8</v>
       </c>
       <c r="D17" t="n">
-        <v>56.13</v>
+        <v>40.64</v>
       </c>
       <c r="E17" t="n">
-        <v>55.76</v>
+        <v>56.39</v>
       </c>
       <c r="F17" t="n">
-        <v>6.71</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>68002990000</v>
+        <v>97768000000</v>
       </c>
       <c r="H17" t="n">
-        <v>1545.42</v>
+        <v>75.84</v>
       </c>
       <c r="I17" t="n">
-        <v>2115.29</v>
+        <v>140.76</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>9.5</v>
+        <v>48.48</v>
       </c>
       <c r="L17" t="n">
-        <v>56.47</v>
+        <v>22.09</v>
       </c>
       <c r="M17" t="n">
-        <v>120.98</v>
+        <v>2.64</v>
       </c>
       <c r="N17" t="n">
-        <v>24.51</v>
+        <v>76.56</v>
       </c>
       <c r="O17" t="n">
-        <v>12.07</v>
+        <v>12.59</v>
       </c>
       <c r="P17" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.67</v>
+        <v>0.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>0.91</v>
       </c>
       <c r="S17" t="n">
-        <v>94.91</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="U17" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NOW</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>95.48</v>
+        <v>216.09</v>
       </c>
       <c r="D18" t="n">
-        <v>41.14</v>
+        <v>56.91</v>
       </c>
       <c r="E18" t="n">
-        <v>56.8</v>
+        <v>34.87</v>
       </c>
       <c r="F18" t="n">
-        <v>7.05</v>
+        <v>3.71</v>
       </c>
       <c r="G18" t="n">
-        <v>98469290000</v>
+        <v>55513520000</v>
       </c>
       <c r="H18" t="n">
-        <v>76.38</v>
+        <v>172.87</v>
       </c>
       <c r="I18" t="n">
-        <v>140.76</v>
+        <v>266.58</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>47.42</v>
+        <v>23.37</v>
       </c>
       <c r="L18" t="n">
-        <v>22.09</v>
+        <v>27.65</v>
       </c>
       <c r="M18" t="n">
-        <v>2.64</v>
+        <v>16.52</v>
       </c>
       <c r="N18" t="n">
-        <v>76.56</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>12.59</v>
+        <v>10.76</v>
       </c>
       <c r="P18" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="R18" t="n">
-        <v>0.91</v>
+        <v>1.92</v>
       </c>
       <c r="S18" t="n">
-        <v>86.27</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="U18" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Construction</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>216.09</v>
+        <v>1965</v>
       </c>
       <c r="D19" t="n">
-        <v>56.91</v>
+        <v>58.36</v>
       </c>
       <c r="E19" t="n">
-        <v>34.87</v>
+        <v>56.72</v>
       </c>
       <c r="F19" t="n">
-        <v>3.71</v>
+        <v>6.82</v>
       </c>
       <c r="G19" t="n">
-        <v>55513520000</v>
+        <v>69172770000</v>
       </c>
       <c r="H19" t="n">
-        <v>172.87</v>
+        <v>1572</v>
       </c>
       <c r="I19" t="n">
-        <v>266.11</v>
+        <v>2115.29</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>23.15</v>
+        <v>7.65</v>
       </c>
       <c r="L19" t="n">
-        <v>27.65</v>
+        <v>56.47</v>
       </c>
       <c r="M19" t="n">
-        <v>16.52</v>
+        <v>120.98</v>
       </c>
       <c r="N19" t="n">
-        <v>90.81999999999999</v>
+        <v>24.51</v>
       </c>
       <c r="O19" t="n">
-        <v>10.76</v>
+        <v>12.07</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.52</v>
+        <v>1.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>92.40000000000001</v>
+        <v>94.91</v>
       </c>
       <c r="T19" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="U19" t="n">
-        <v>56.9</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="20">
@@ -1785,31 +1785,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>374.68</v>
+        <v>385.6</v>
       </c>
       <c r="D20" t="n">
-        <v>63.89</v>
+        <v>65.64</v>
       </c>
       <c r="E20" t="n">
-        <v>252.55</v>
+        <v>259.91</v>
       </c>
       <c r="F20" t="n">
-        <v>64.13</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>64223130000</v>
+        <v>66094910000</v>
       </c>
       <c r="H20" t="n">
-        <v>299.74</v>
+        <v>308.48</v>
       </c>
       <c r="I20" t="n">
-        <v>253.06</v>
+        <v>257.11</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-32.46</v>
+        <v>-33.32</v>
       </c>
       <c r="L20" t="n">
         <v>93.40000000000001</v>
@@ -1827,292 +1827,286 @@
         <v>0.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="R20" t="n">
         <v>18.28</v>
       </c>
       <c r="S20" t="n">
-        <v>71.3</v>
+        <v>71.34</v>
       </c>
       <c r="T20" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U20" t="n">
-        <v>56.7</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Server and Rack Systems</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48.2</v>
+        <v>182.64</v>
       </c>
       <c r="D21" t="n">
-        <v>62.47</v>
+        <v>42.22</v>
       </c>
       <c r="E21" t="n">
-        <v>46.21</v>
+        <v>31.35</v>
       </c>
       <c r="F21" t="n">
-        <v>1.64</v>
+        <v>7.8</v>
       </c>
       <c r="G21" t="n">
-        <v>63826610000</v>
+        <v>525281020000</v>
       </c>
       <c r="H21" t="n">
-        <v>38.56</v>
+        <v>146.11</v>
       </c>
       <c r="I21" t="n">
-        <v>68.59</v>
+        <v>255.38</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>42.3</v>
+        <v>39.83</v>
       </c>
       <c r="L21" t="n">
-        <v>40.64</v>
+        <v>20.63</v>
       </c>
       <c r="M21" t="n">
-        <v>150.91</v>
+        <v>21.47</v>
       </c>
       <c r="N21" t="n">
-        <v>31.36</v>
+        <v>73.55</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>25.21</v>
       </c>
       <c r="P21" t="n">
-        <v>0.84</v>
+        <v>3.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.43</v>
+        <v>1.69</v>
       </c>
       <c r="R21" t="n">
-        <v>0.38</v>
+        <v>40.54</v>
       </c>
       <c r="S21" t="n">
-        <v>92.45</v>
+        <v>43.83</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="U21" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Server and Rack Systems</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>183.53</v>
+        <v>49.33</v>
       </c>
       <c r="D22" t="n">
-        <v>42.62</v>
+        <v>64.39</v>
       </c>
       <c r="E22" t="n">
-        <v>31.5</v>
+        <v>47.3</v>
       </c>
       <c r="F22" t="n">
-        <v>7.84</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="n">
-        <v>527840699999</v>
+        <v>65322960000</v>
       </c>
       <c r="H22" t="n">
-        <v>146.82</v>
+        <v>39.46</v>
       </c>
       <c r="I22" t="n">
-        <v>255.38</v>
+        <v>68.59</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>39.15</v>
+        <v>39.04</v>
       </c>
       <c r="L22" t="n">
-        <v>20.63</v>
+        <v>40.64</v>
       </c>
       <c r="M22" t="n">
-        <v>21.47</v>
+        <v>150.91</v>
       </c>
       <c r="N22" t="n">
-        <v>73.55</v>
+        <v>31.36</v>
       </c>
       <c r="O22" t="n">
-        <v>25.21</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>3.63</v>
+        <v>0.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="R22" t="n">
-        <v>40.54</v>
+        <v>0.38</v>
       </c>
       <c r="S22" t="n">
-        <v>43.83</v>
+        <v>92.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>56</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1048.86</v>
+        <v>123.25</v>
       </c>
       <c r="D23" t="n">
-        <v>59.46</v>
-      </c>
-      <c r="E23" t="n">
-        <v>30.56</v>
+        <v>39.5</v>
       </c>
       <c r="F23" t="n">
-        <v>7.16</v>
+        <v>6.28</v>
       </c>
       <c r="G23" t="n">
-        <v>281849660000</v>
+        <v>19930700000</v>
       </c>
       <c r="H23" t="n">
-        <v>839.09</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1227.4</v>
-      </c>
-      <c r="J23" t="b">
-        <v>0</v>
+        <v>192.67</v>
       </c>
       <c r="K23" t="n">
-        <v>17.02</v>
+        <v>56.32</v>
       </c>
       <c r="L23" t="n">
-        <v>15.98</v>
+        <v>25.43</v>
       </c>
       <c r="M23" t="n">
-        <v>1816.17</v>
+        <v>-224.81</v>
       </c>
       <c r="N23" t="n">
-        <v>20.16</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>23.83</v>
+        <v>-2.44</v>
       </c>
       <c r="P23" t="n">
-        <v>0.21</v>
+        <v>0.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="R23" t="n">
-        <v>0.15</v>
+        <v>35.18</v>
       </c>
       <c r="S23" t="n">
-        <v>78.51000000000001</v>
+        <v>54.19</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="U23" t="n">
-        <v>54.7</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>164.93</v>
+        <v>1073</v>
       </c>
       <c r="D24" t="n">
-        <v>55.5</v>
+        <v>62.1</v>
       </c>
       <c r="E24" t="n">
-        <v>56.48</v>
+        <v>31.26</v>
       </c>
       <c r="F24" t="n">
-        <v>21.39</v>
+        <v>7.33</v>
       </c>
       <c r="G24" t="n">
-        <v>207680280000</v>
+        <v>288336560000</v>
       </c>
       <c r="H24" t="n">
-        <v>131.94</v>
+        <v>858.4</v>
       </c>
       <c r="I24" t="n">
-        <v>190.3</v>
+        <v>1227.4</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>15.38</v>
+        <v>14.39</v>
       </c>
       <c r="L24" t="n">
-        <v>35.13</v>
+        <v>15.98</v>
       </c>
       <c r="M24" t="n">
-        <v>26.22</v>
+        <v>1816.17</v>
       </c>
       <c r="N24" t="n">
-        <v>63.54</v>
+        <v>20.16</v>
       </c>
       <c r="O24" t="n">
-        <v>38.32</v>
+        <v>23.83</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>17.07</v>
+        <v>0.15</v>
       </c>
       <c r="S24" t="n">
-        <v>72.05</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>1.12</v>
+        <v>1.69</v>
       </c>
       <c r="U24" t="n">
         <v>53.9</v>
@@ -2121,340 +2115,346 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>124.38</v>
+        <v>167.92</v>
       </c>
       <c r="D25" t="n">
-        <v>40.13</v>
+        <v>57.71</v>
+      </c>
+      <c r="E25" t="n">
+        <v>57.5</v>
       </c>
       <c r="F25" t="n">
-        <v>6.34</v>
+        <v>21.78</v>
       </c>
       <c r="G25" t="n">
-        <v>20113430000</v>
+        <v>211450970000</v>
       </c>
       <c r="H25" t="n">
-        <v>99.5</v>
+        <v>134.34</v>
       </c>
       <c r="I25" t="n">
-        <v>192.67</v>
+        <v>190.3</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>54.9</v>
+        <v>13.33</v>
       </c>
       <c r="L25" t="n">
-        <v>25.43</v>
+        <v>35.13</v>
       </c>
       <c r="M25" t="n">
-        <v>-224.81</v>
+        <v>26.22</v>
       </c>
       <c r="N25" t="n">
-        <v>76.29000000000001</v>
+        <v>63.54</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.44</v>
+        <v>38.32</v>
       </c>
       <c r="P25" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.97</v>
+        <v>1.6</v>
       </c>
       <c r="R25" t="n">
-        <v>35.18</v>
+        <v>17.07</v>
       </c>
       <c r="S25" t="n">
-        <v>54.2</v>
+        <v>72.02</v>
       </c>
       <c r="T25" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="U25" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>317.58</v>
+        <v>224.23</v>
       </c>
       <c r="D26" t="n">
-        <v>51.37</v>
+        <v>53.2</v>
       </c>
       <c r="E26" t="n">
-        <v>79.72</v>
+        <v>598.42</v>
       </c>
       <c r="F26" t="n">
-        <v>11.25</v>
+        <v>21.74</v>
       </c>
       <c r="G26" t="n">
-        <v>121985280000</v>
+        <v>79816140000</v>
       </c>
       <c r="H26" t="n">
-        <v>254.06</v>
+        <v>179.38</v>
       </c>
       <c r="I26" t="n">
-        <v>380.63</v>
+        <v>242.39</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>19.85</v>
+        <v>8.1</v>
       </c>
       <c r="L26" t="n">
-        <v>30.13</v>
+        <v>32.15</v>
       </c>
       <c r="M26" t="n">
-        <v>135.9</v>
+        <v>115.46</v>
       </c>
       <c r="N26" t="n">
-        <v>35</v>
+        <v>79.86</v>
       </c>
       <c r="O26" t="n">
-        <v>14.37</v>
+        <v>3.69</v>
       </c>
       <c r="P26" t="n">
-        <v>0.77</v>
+        <v>0.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.71</v>
+        <v>9.06</v>
       </c>
       <c r="S26" t="n">
-        <v>84.73</v>
+        <v>81.38</v>
       </c>
       <c r="T26" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="U26" t="n">
-        <v>53.7</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Security</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOD</t>
+          <t>ALRM</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>283.88</v>
+        <v>45.28</v>
       </c>
       <c r="D27" t="n">
-        <v>53.87</v>
+        <v>50.66</v>
       </c>
       <c r="E27" t="n">
-        <v>126.82</v>
+        <v>18.79</v>
       </c>
       <c r="F27" t="n">
-        <v>4.71</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>14993340000</v>
+        <v>2239570000</v>
       </c>
       <c r="H27" t="n">
-        <v>227.1</v>
+        <v>36.22</v>
       </c>
       <c r="I27" t="n">
-        <v>351.75</v>
+        <v>59</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>23.91</v>
+        <v>30.3</v>
       </c>
       <c r="L27" t="n">
-        <v>47.47</v>
+        <v>11.04</v>
       </c>
       <c r="M27" t="n">
-        <v>47.51</v>
+        <v>-10.25</v>
       </c>
       <c r="N27" t="n">
-        <v>23.19</v>
+        <v>62.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3.82</v>
+        <v>12.36</v>
       </c>
       <c r="P27" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.66</v>
+        <v>0.78</v>
       </c>
       <c r="R27" t="n">
-        <v>2.15</v>
+        <v>5.93</v>
       </c>
       <c r="S27" t="n">
-        <v>106.36</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Security</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ALRM</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>45.23</v>
+        <v>328.98</v>
       </c>
       <c r="D28" t="n">
-        <v>50.34</v>
+        <v>55.37</v>
       </c>
       <c r="E28" t="n">
-        <v>18.77</v>
+        <v>82.59</v>
       </c>
       <c r="F28" t="n">
-        <v>2.16</v>
+        <v>11.65</v>
       </c>
       <c r="G28" t="n">
-        <v>2237100000</v>
+        <v>126364130000</v>
       </c>
       <c r="H28" t="n">
-        <v>36.18</v>
+        <v>263.18</v>
       </c>
       <c r="I28" t="n">
-        <v>59</v>
+        <v>380.63</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>30.44</v>
+        <v>15.7</v>
       </c>
       <c r="L28" t="n">
-        <v>11.04</v>
+        <v>30.13</v>
       </c>
       <c r="M28" t="n">
-        <v>-10.25</v>
+        <v>135.9</v>
       </c>
       <c r="N28" t="n">
-        <v>62.66</v>
+        <v>35</v>
       </c>
       <c r="O28" t="n">
-        <v>12.36</v>
+        <v>14.37</v>
       </c>
       <c r="P28" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.78</v>
+        <v>2.03</v>
       </c>
       <c r="R28" t="n">
-        <v>5.93</v>
+        <v>1.71</v>
       </c>
       <c r="S28" t="n">
-        <v>97.51000000000001</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="U28" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MOD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>226.63</v>
+        <v>288.5</v>
       </c>
       <c r="D29" t="n">
-        <v>54.78</v>
+        <v>55.59</v>
       </c>
       <c r="E29" t="n">
-        <v>604.83</v>
+        <v>128.89</v>
       </c>
       <c r="F29" t="n">
-        <v>21.97</v>
+        <v>4.79</v>
       </c>
       <c r="G29" t="n">
-        <v>80671260000</v>
+        <v>15237360000</v>
       </c>
       <c r="H29" t="n">
-        <v>181.3</v>
+        <v>230.8</v>
       </c>
       <c r="I29" t="n">
-        <v>242.39</v>
+        <v>351.75</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>6.95</v>
+        <v>21.92</v>
       </c>
       <c r="L29" t="n">
-        <v>32.15</v>
+        <v>47.47</v>
       </c>
       <c r="M29" t="n">
-        <v>115.46</v>
+        <v>47.51</v>
       </c>
       <c r="N29" t="n">
-        <v>79.86</v>
+        <v>23.19</v>
       </c>
       <c r="O29" t="n">
-        <v>3.69</v>
+        <v>3.82</v>
       </c>
       <c r="P29" t="n">
-        <v>0.32</v>
+        <v>0.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R29" t="n">
-        <v>9.06</v>
+        <v>2.15</v>
       </c>
       <c r="S29" t="n">
-        <v>81.38</v>
+        <v>106.36</v>
       </c>
       <c r="T29" t="n">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>52.4</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="30">
@@ -2465,65 +2465,65 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>MWA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>110.29</v>
+        <v>25.74</v>
       </c>
       <c r="D30" t="n">
-        <v>47.39</v>
+        <v>48.53</v>
       </c>
       <c r="E30" t="n">
-        <v>27.4</v>
+        <v>19.53</v>
       </c>
       <c r="F30" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="G30" t="n">
-        <v>26215210000</v>
+        <v>4027560000</v>
       </c>
       <c r="H30" t="n">
-        <v>88.23</v>
+        <v>20.59</v>
       </c>
       <c r="I30" t="n">
-        <v>152.31</v>
+        <v>32.2</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>38.1</v>
+        <v>25.1</v>
       </c>
       <c r="L30" t="n">
-        <v>2.71</v>
+        <v>5.52</v>
       </c>
       <c r="M30" t="n">
-        <v>14.41</v>
+        <v>15.29</v>
       </c>
       <c r="N30" t="n">
-        <v>38.48</v>
+        <v>37.58</v>
       </c>
       <c r="O30" t="n">
-        <v>10.8</v>
+        <v>14.17</v>
       </c>
       <c r="P30" t="n">
-        <v>0.19</v>
+        <v>0.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="R30" t="n">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="S30" t="n">
-        <v>95.73999999999999</v>
+        <v>95.95</v>
       </c>
       <c r="T30" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>52.4</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>827.5</v>
+        <v>835.75</v>
       </c>
       <c r="D31" t="n">
-        <v>46.79</v>
+        <v>49.01</v>
       </c>
       <c r="E31" t="n">
-        <v>27.69</v>
+        <v>27.97</v>
       </c>
       <c r="F31" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="G31" t="n">
-        <v>36774330000</v>
+        <v>37140960000</v>
       </c>
       <c r="H31" t="n">
-        <v>662</v>
+        <v>668.6</v>
       </c>
       <c r="I31" t="n">
         <v>1000.14</v>
@@ -2562,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>20.86</v>
+        <v>19.67</v>
       </c>
       <c r="L31" t="n">
         <v>19.67</v>
@@ -2580,7 +2580,7 @@
         <v>0.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R31" t="n">
         <v>0.74</v>
@@ -2592,7 +2592,7 @@
         <v>1.91</v>
       </c>
       <c r="U31" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="32">
@@ -2603,197 +2603,197 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MWA</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>25.65</v>
+        <v>112.01</v>
       </c>
       <c r="D32" t="n">
-        <v>47.42</v>
+        <v>52.13</v>
       </c>
       <c r="E32" t="n">
-        <v>19.46</v>
+        <v>27.83</v>
       </c>
       <c r="F32" t="n">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="G32" t="n">
-        <v>4013490000</v>
+        <v>26624050000</v>
       </c>
       <c r="H32" t="n">
-        <v>20.52</v>
+        <v>89.61</v>
       </c>
       <c r="I32" t="n">
-        <v>32.2</v>
+        <v>152.31</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>25.54</v>
+        <v>35.98</v>
       </c>
       <c r="L32" t="n">
-        <v>5.52</v>
+        <v>2.71</v>
       </c>
       <c r="M32" t="n">
-        <v>15.29</v>
+        <v>14.41</v>
       </c>
       <c r="N32" t="n">
-        <v>37.58</v>
+        <v>38.48</v>
       </c>
       <c r="O32" t="n">
-        <v>14.17</v>
+        <v>10.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0.42</v>
+        <v>0.19</v>
       </c>
       <c r="Q32" t="n">
         <v>1.03</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="S32" t="n">
-        <v>95.95</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U32" t="n">
-        <v>52.3</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Memory and Storage</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>712.13</v>
+        <v>420</v>
       </c>
       <c r="D33" t="n">
-        <v>75.73</v>
-      </c>
-      <c r="E33" t="n">
-        <v>42.51</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>20.84</v>
+        <v>4.09</v>
       </c>
       <c r="G33" t="n">
-        <v>245458490000</v>
+        <v>19065910000</v>
       </c>
       <c r="H33" t="n">
-        <v>569.7</v>
+        <v>336</v>
       </c>
       <c r="I33" t="n">
-        <v>560</v>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
+        <v>478.62</v>
       </c>
       <c r="K33" t="n">
-        <v>-21.36</v>
+        <v>13.96</v>
       </c>
       <c r="L33" t="n">
-        <v>45.47</v>
+        <v>21.64</v>
       </c>
       <c r="M33" t="n">
-        <v>483.37</v>
+        <v>145.11</v>
       </c>
       <c r="N33" t="n">
-        <v>45.39</v>
+        <v>63.43</v>
       </c>
       <c r="O33" t="n">
-        <v>54.28</v>
+        <v>-0.45</v>
       </c>
       <c r="P33" t="n">
-        <v>0.18</v>
+        <v>6.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.11</v>
+        <v>1.57</v>
       </c>
       <c r="R33" t="n">
-        <v>0.95</v>
+        <v>1.84</v>
       </c>
       <c r="S33" t="n">
-        <v>97.73999999999999</v>
+        <v>103.78</v>
       </c>
       <c r="T33" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="U33" t="n">
-        <v>52.1</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Heating and Cooling</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>AAON</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>409.81</v>
+        <v>134.7</v>
       </c>
       <c r="D34" t="n">
-        <v>63.25</v>
+        <v>55.35</v>
+      </c>
+      <c r="E34" t="n">
+        <v>94.75</v>
       </c>
       <c r="F34" t="n">
-        <v>3.99</v>
+        <v>6.82</v>
       </c>
       <c r="G34" t="n">
-        <v>18603330000</v>
+        <v>11033510000</v>
       </c>
       <c r="H34" t="n">
-        <v>327.85</v>
+        <v>107.76</v>
       </c>
       <c r="I34" t="n">
-        <v>478.62</v>
+        <v>149.75</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>16.79</v>
+        <v>11.17</v>
       </c>
       <c r="L34" t="n">
-        <v>21.64</v>
+        <v>54.3</v>
       </c>
       <c r="M34" t="n">
-        <v>145.11</v>
+        <v>36.23</v>
       </c>
       <c r="N34" t="n">
-        <v>63.43</v>
+        <v>24.54</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.45</v>
+        <v>7.3</v>
       </c>
       <c r="P34" t="n">
-        <v>6.34</v>
+        <v>0.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.84</v>
+        <v>16.68</v>
       </c>
       <c r="S34" t="n">
-        <v>103.78</v>
+        <v>88.28</v>
       </c>
       <c r="T34" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="U34" t="n">
-        <v>51.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="35">
@@ -2808,28 +2808,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>125.44</v>
+        <v>126.99</v>
       </c>
       <c r="D35" t="n">
-        <v>50.25</v>
+        <v>53.05</v>
       </c>
       <c r="E35" t="n">
-        <v>137.74</v>
+        <v>139.44</v>
       </c>
       <c r="F35" t="n">
-        <v>5.15</v>
+        <v>5.21</v>
       </c>
       <c r="G35" t="n">
-        <v>37321500000</v>
+        <v>37782660000</v>
       </c>
       <c r="H35" t="n">
-        <v>100.35</v>
+        <v>101.59</v>
       </c>
       <c r="I35" t="n">
         <v>131.55</v>
       </c>
       <c r="K35" t="n">
-        <v>4.87</v>
+        <v>3.59</v>
       </c>
       <c r="L35" t="n">
         <v>21.58</v>
@@ -2856,751 +2856,751 @@
         <v>1.5</v>
       </c>
       <c r="U35" t="n">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Memory and Storage</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>187.08</v>
+        <v>754.89</v>
       </c>
       <c r="D36" t="n">
-        <v>48.63</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>49.48</v>
+        <v>45.06</v>
       </c>
       <c r="F36" t="n">
-        <v>10.24</v>
+        <v>22.09</v>
       </c>
       <c r="G36" t="n">
-        <v>65741039999</v>
+        <v>260197100000</v>
       </c>
       <c r="H36" t="n">
-        <v>149.66</v>
+        <v>603.91</v>
       </c>
       <c r="I36" t="n">
-        <v>219.17</v>
+        <v>560</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>17.15</v>
+        <v>-25.82</v>
       </c>
       <c r="L36" t="n">
-        <v>16.16</v>
+        <v>45.47</v>
       </c>
       <c r="M36" t="n">
-        <v>67.62</v>
+        <v>483.37</v>
       </c>
       <c r="N36" t="n">
-        <v>25.66</v>
+        <v>45.39</v>
       </c>
       <c r="O36" t="n">
-        <v>20.83</v>
+        <v>54.28</v>
       </c>
       <c r="P36" t="n">
-        <v>0.82</v>
+        <v>0.18</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="R36" t="n">
-        <v>0.03</v>
+        <v>0.95</v>
       </c>
       <c r="S36" t="n">
-        <v>99.48</v>
+        <v>97.73</v>
       </c>
       <c r="T36" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>51.3</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Cloud</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>280.91</v>
+        <v>189.12</v>
       </c>
       <c r="D37" t="n">
-        <v>68.56999999999999</v>
+        <v>51.42</v>
       </c>
       <c r="E37" t="n">
-        <v>93.72</v>
+        <v>50.02</v>
       </c>
       <c r="F37" t="n">
-        <v>80.52</v>
+        <v>10.36</v>
       </c>
       <c r="G37" t="n">
-        <v>70691120000</v>
+        <v>66457920000</v>
       </c>
       <c r="H37" t="n">
-        <v>224.73</v>
+        <v>151.3</v>
       </c>
       <c r="I37" t="n">
-        <v>255.29</v>
+        <v>219.17</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.119999999999999</v>
+        <v>15.89</v>
       </c>
       <c r="L37" t="n">
-        <v>621.52</v>
+        <v>16.16</v>
       </c>
       <c r="M37" t="n">
-        <v>521.4</v>
+        <v>67.62</v>
       </c>
       <c r="N37" t="n">
-        <v>7.48</v>
+        <v>25.66</v>
       </c>
       <c r="O37" t="n">
-        <v>95.27</v>
+        <v>20.83</v>
       </c>
       <c r="P37" t="n">
-        <v>1.31</v>
+        <v>0.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.28</v>
+        <v>1.04</v>
       </c>
       <c r="R37" t="n">
-        <v>19.73</v>
+        <v>0.03</v>
       </c>
       <c r="S37" t="n">
-        <v>50.26</v>
+        <v>99.48</v>
       </c>
       <c r="T37" t="n">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="U37" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Heating and Cooling</t>
+          <t>AI Cloud</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AAON</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>133.36</v>
+        <v>294</v>
       </c>
       <c r="D38" t="n">
-        <v>54.18</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>93.81</v>
+        <v>98.09</v>
       </c>
       <c r="F38" t="n">
-        <v>6.76</v>
+        <v>84.28</v>
       </c>
       <c r="G38" t="n">
-        <v>10923740000</v>
+        <v>73985230000</v>
       </c>
       <c r="H38" t="n">
-        <v>106.69</v>
+        <v>235.2</v>
       </c>
       <c r="I38" t="n">
-        <v>149.75</v>
+        <v>255.29</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>12.29</v>
+        <v>-13.17</v>
       </c>
       <c r="L38" t="n">
-        <v>54.3</v>
+        <v>621.52</v>
       </c>
       <c r="M38" t="n">
-        <v>36.23</v>
+        <v>521.4</v>
       </c>
       <c r="N38" t="n">
-        <v>24.54</v>
+        <v>7.48</v>
       </c>
       <c r="O38" t="n">
-        <v>7.3</v>
+        <v>95.27</v>
       </c>
       <c r="P38" t="n">
-        <v>0.49</v>
+        <v>1.31</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.41</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
-        <v>16.68</v>
+        <v>19.73</v>
       </c>
       <c r="S38" t="n">
-        <v>88.28</v>
+        <v>50.29</v>
       </c>
       <c r="T38" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="U38" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Networking</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>378.85</v>
+        <v>111.64</v>
       </c>
       <c r="D39" t="n">
-        <v>51.15</v>
+        <v>54.46</v>
       </c>
       <c r="E39" t="n">
-        <v>180.87</v>
+        <v>81.09</v>
       </c>
       <c r="F39" t="n">
-        <v>11.23</v>
+        <v>6.48</v>
       </c>
       <c r="G39" t="n">
-        <v>74117960000</v>
+        <v>19403860000</v>
       </c>
       <c r="H39" t="n">
-        <v>303.08</v>
+        <v>89.31</v>
       </c>
       <c r="I39" t="n">
-        <v>388.09</v>
+        <v>120.2</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>2.44</v>
+        <v>7.67</v>
       </c>
       <c r="L39" t="n">
-        <v>20.55</v>
+        <v>11.19</v>
       </c>
       <c r="M39" t="n">
-        <v>990.95</v>
+        <v>20.1</v>
       </c>
       <c r="N39" t="n">
-        <v>37.93</v>
+        <v>77.44</v>
       </c>
       <c r="O39" t="n">
-        <v>6.07</v>
+        <v>8.24</v>
       </c>
       <c r="P39" t="n">
-        <v>0.32</v>
+        <v>0.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R39" t="n">
-        <v>4.45</v>
+        <v>4.97</v>
       </c>
       <c r="S39" t="n">
-        <v>88.13</v>
+        <v>93.41</v>
       </c>
       <c r="T39" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="U39" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Networking</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>143.62</v>
+        <v>390.6</v>
       </c>
       <c r="D40" t="n">
-        <v>52.21</v>
+        <v>53.54</v>
       </c>
       <c r="E40" t="n">
-        <v>25.69</v>
+        <v>186.48</v>
       </c>
       <c r="F40" t="n">
-        <v>3.59</v>
+        <v>11.57</v>
       </c>
       <c r="G40" t="n">
-        <v>87624800000</v>
+        <v>76416720000</v>
       </c>
       <c r="H40" t="n">
-        <v>114.9</v>
+        <v>312.48</v>
       </c>
       <c r="I40" t="n">
-        <v>157.1</v>
+        <v>388.09</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>9.390000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="L40" t="n">
-        <v>8.210000000000001</v>
+        <v>20.55</v>
       </c>
       <c r="M40" t="n">
-        <v>38.05</v>
+        <v>990.95</v>
       </c>
       <c r="N40" t="n">
-        <v>36.49</v>
+        <v>37.93</v>
       </c>
       <c r="O40" t="n">
-        <v>14.45</v>
+        <v>6.07</v>
       </c>
       <c r="P40" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.32</v>
+        <v>2.03</v>
       </c>
       <c r="R40" t="n">
-        <v>0.34</v>
+        <v>4.45</v>
       </c>
       <c r="S40" t="n">
-        <v>92.81999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="T40" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="U40" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Compute Chips</t>
+          <t>AI Cybersecurity</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>512.48</v>
+        <v>679.99</v>
       </c>
       <c r="D41" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="E41" t="n">
-        <v>168.2</v>
+        <v>57.12</v>
       </c>
       <c r="F41" t="n">
-        <v>22.31</v>
+        <v>33.98</v>
       </c>
       <c r="G41" t="n">
-        <v>835650160000</v>
+        <v>173101520000</v>
       </c>
       <c r="H41" t="n">
-        <v>409.98</v>
+        <v>543.99</v>
       </c>
       <c r="I41" t="n">
-        <v>496.32</v>
-      </c>
-      <c r="J41" t="b">
-        <v>0</v>
+        <v>720.9299999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.15</v>
+        <v>6.02</v>
       </c>
       <c r="L41" t="n">
-        <v>37.85</v>
+        <v>25.57</v>
       </c>
       <c r="M41" t="n">
-        <v>92.25</v>
+        <v>124.28</v>
       </c>
       <c r="N41" t="n">
-        <v>47.09</v>
+        <v>74.89</v>
       </c>
       <c r="O41" t="n">
-        <v>13.37</v>
+        <v>-0.89</v>
       </c>
       <c r="P41" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.49</v>
+        <v>1.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0.49</v>
+        <v>3.56</v>
       </c>
       <c r="S41" t="n">
-        <v>68.29000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="T41" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="U41" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>113.03</v>
+        <v>146.97</v>
       </c>
       <c r="D42" t="n">
-        <v>55.91</v>
+        <v>56.64</v>
       </c>
       <c r="E42" t="n">
-        <v>82.09999999999999</v>
+        <v>26.29</v>
       </c>
       <c r="F42" t="n">
-        <v>6.56</v>
+        <v>3.67</v>
       </c>
       <c r="G42" t="n">
-        <v>19645440000</v>
+        <v>89668690000</v>
       </c>
       <c r="H42" t="n">
-        <v>90.42</v>
+        <v>117.58</v>
       </c>
       <c r="I42" t="n">
-        <v>120.2</v>
+        <v>157.1</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>6.34</v>
+        <v>6.89</v>
       </c>
       <c r="L42" t="n">
-        <v>11.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>20.1</v>
+        <v>38.05</v>
       </c>
       <c r="N42" t="n">
-        <v>77.44</v>
+        <v>36.49</v>
       </c>
       <c r="O42" t="n">
-        <v>8.24</v>
+        <v>14.45</v>
       </c>
       <c r="P42" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.8</v>
+        <v>1.31</v>
       </c>
       <c r="R42" t="n">
-        <v>4.97</v>
+        <v>0.34</v>
       </c>
       <c r="S42" t="n">
-        <v>93.41</v>
+        <v>92.81</v>
       </c>
       <c r="T42" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="U42" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Compute Chips</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>284.99</v>
+        <v>531</v>
       </c>
       <c r="D43" t="n">
-        <v>55.12</v>
+        <v>60.35</v>
+      </c>
+      <c r="E43" t="n">
+        <v>174.28</v>
       </c>
       <c r="F43" t="n">
-        <v>33.1</v>
+        <v>23.12</v>
       </c>
       <c r="G43" t="n">
-        <v>81063660000</v>
+        <v>865848910000</v>
       </c>
       <c r="H43" t="n">
-        <v>227.99</v>
+        <v>424.8</v>
       </c>
       <c r="I43" t="n">
-        <v>279.01</v>
+        <v>496.32</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.1</v>
+        <v>-6.53</v>
       </c>
       <c r="L43" t="n">
-        <v>130.37</v>
+        <v>37.85</v>
       </c>
       <c r="M43" t="n">
-        <v>313.73</v>
+        <v>92.25</v>
       </c>
       <c r="N43" t="n">
-        <v>31.08</v>
+        <v>47.09</v>
       </c>
       <c r="O43" t="n">
-        <v>0.25</v>
+        <v>13.37</v>
       </c>
       <c r="P43" t="n">
-        <v>3.2</v>
+        <v>0.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>2.48</v>
       </c>
       <c r="R43" t="n">
-        <v>6.31</v>
+        <v>0.49</v>
       </c>
       <c r="S43" t="n">
-        <v>85.98999999999999</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>2.26</v>
+        <v>1.49</v>
       </c>
       <c r="U43" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Cybersecurity</t>
+          <t>AI Insurance and Risk</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>RYAN</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>682.96</v>
+        <v>35.28</v>
       </c>
       <c r="D44" t="n">
-        <v>57.83</v>
+        <v>59.05</v>
+      </c>
+      <c r="E44" t="n">
+        <v>47.94</v>
       </c>
       <c r="F44" t="n">
-        <v>34.13</v>
+        <v>2.94</v>
       </c>
       <c r="G44" t="n">
-        <v>173857600000</v>
+        <v>9301900000</v>
       </c>
       <c r="H44" t="n">
-        <v>546.37</v>
+        <v>28.22</v>
       </c>
       <c r="I44" t="n">
-        <v>720.9299999999999</v>
+        <v>41.56</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>5.56</v>
+        <v>17.8</v>
       </c>
       <c r="L44" t="n">
-        <v>25.57</v>
+        <v>14.57</v>
       </c>
       <c r="M44" t="n">
-        <v>124.28</v>
-      </c>
-      <c r="N44" t="n">
-        <v>74.89</v>
+        <v>158.3</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.89</v>
+        <v>3.43</v>
       </c>
       <c r="P44" t="n">
-        <v>0.18</v>
+        <v>5.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.26</v>
+        <v>0.61</v>
       </c>
       <c r="R44" t="n">
-        <v>3.56</v>
+        <v>12.65</v>
       </c>
       <c r="S44" t="n">
-        <v>71.22</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="T44" t="n">
-        <v>1.59</v>
+        <v>2.29</v>
       </c>
       <c r="U44" t="n">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Power Generation</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>158.83</v>
+        <v>296.64</v>
       </c>
       <c r="D45" t="n">
-        <v>56.79</v>
-      </c>
-      <c r="E45" t="n">
-        <v>26.52</v>
+        <v>58.22</v>
       </c>
       <c r="F45" t="n">
-        <v>3.25</v>
+        <v>34.45</v>
       </c>
       <c r="G45" t="n">
-        <v>53554690000</v>
+        <v>84377440000</v>
       </c>
       <c r="H45" t="n">
-        <v>127.06</v>
+        <v>237.31</v>
       </c>
       <c r="I45" t="n">
-        <v>230.29</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
+        <v>279.01</v>
       </c>
       <c r="K45" t="n">
-        <v>44.99</v>
+        <v>-5.94</v>
       </c>
       <c r="L45" t="n">
-        <v>-10</v>
+        <v>130.37</v>
       </c>
       <c r="M45" t="n">
-        <v>407.29</v>
+        <v>313.73</v>
       </c>
       <c r="N45" t="n">
-        <v>14.65</v>
+        <v>31.08</v>
       </c>
       <c r="O45" t="n">
-        <v>12.45</v>
+        <v>0.25</v>
       </c>
       <c r="P45" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.41</v>
+        <v>3.74</v>
       </c>
       <c r="R45" t="n">
-        <v>0.97</v>
+        <v>6.31</v>
       </c>
       <c r="S45" t="n">
-        <v>90.03</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="T45" t="n">
-        <v>1.3</v>
+        <v>2.26</v>
       </c>
       <c r="U45" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Insurance and Risk</t>
+          <t>AI Power Generation</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RYAN</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>35.28</v>
+        <v>160.98</v>
       </c>
       <c r="D46" t="n">
-        <v>59.05</v>
+        <v>58.61</v>
       </c>
       <c r="E46" t="n">
-        <v>47.94</v>
+        <v>26.88</v>
       </c>
       <c r="F46" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="G46" t="n">
-        <v>9301900000</v>
+        <v>54279630000</v>
       </c>
       <c r="H46" t="n">
-        <v>28.22</v>
+        <v>128.78</v>
       </c>
       <c r="I46" t="n">
-        <v>41.56</v>
+        <v>230.29</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>17.8</v>
+        <v>43.06</v>
       </c>
       <c r="L46" t="n">
-        <v>14.57</v>
+        <v>-10</v>
       </c>
       <c r="M46" t="n">
-        <v>158.3</v>
+        <v>407.29</v>
+      </c>
+      <c r="N46" t="n">
+        <v>14.65</v>
       </c>
       <c r="O46" t="n">
-        <v>3.43</v>
+        <v>12.45</v>
       </c>
       <c r="P46" t="n">
-        <v>5.88</v>
+        <v>3.56</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.62</v>
+        <v>1.41</v>
       </c>
       <c r="R46" t="n">
-        <v>12.65</v>
+        <v>0.97</v>
       </c>
       <c r="S46" t="n">
-        <v>87.93000000000001</v>
+        <v>90.03</v>
       </c>
       <c r="T46" t="n">
-        <v>2.29</v>
+        <v>1.3</v>
       </c>
       <c r="U46" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="47">
@@ -3675,139 +3675,139 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Grid and Power Transmission</t>
+          <t>AI Software and Platforms</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>714.85</v>
+        <v>40.92</v>
       </c>
       <c r="D48" t="n">
-        <v>52.65</v>
+        <v>51.34</v>
       </c>
       <c r="E48" t="n">
-        <v>98.06999999999999</v>
+        <v>76.33</v>
       </c>
       <c r="F48" t="n">
-        <v>3.56</v>
+        <v>5.91</v>
       </c>
       <c r="G48" t="n">
-        <v>107270490000</v>
+        <v>11927180000</v>
       </c>
       <c r="H48" t="n">
-        <v>571.88</v>
+        <v>32.74</v>
       </c>
       <c r="I48" t="n">
-        <v>802.79</v>
+        <v>45.41</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>12.3</v>
+        <v>10.97</v>
       </c>
       <c r="L48" t="n">
-        <v>26.33</v>
+        <v>19.44</v>
       </c>
       <c r="M48" t="n">
-        <v>51.81</v>
+        <v>-54.84</v>
       </c>
       <c r="N48" t="n">
-        <v>13.3</v>
+        <v>81.56</v>
       </c>
       <c r="O48" t="n">
-        <v>3.67</v>
+        <v>8.06</v>
       </c>
       <c r="P48" t="n">
-        <v>0.7</v>
+        <v>0.06</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="S48" t="n">
-        <v>93.23999999999999</v>
+        <v>101.95</v>
       </c>
       <c r="T48" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="U48" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Software and Platforms</t>
+          <t>AI Grid and Power Transmission</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>41.25</v>
+        <v>725</v>
       </c>
       <c r="D49" t="n">
-        <v>52.98</v>
+        <v>54.99</v>
       </c>
       <c r="E49" t="n">
-        <v>76.94</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>5.96</v>
+        <v>3.61</v>
       </c>
       <c r="G49" t="n">
-        <v>12023370000</v>
+        <v>108793600000</v>
       </c>
       <c r="H49" t="n">
-        <v>33</v>
+        <v>580</v>
       </c>
       <c r="I49" t="n">
-        <v>45.25</v>
+        <v>802.79</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>9.699999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="L49" t="n">
-        <v>19.44</v>
+        <v>26.33</v>
       </c>
       <c r="M49" t="n">
-        <v>-54.84</v>
+        <v>51.81</v>
       </c>
       <c r="N49" t="n">
-        <v>81.56</v>
+        <v>13.3</v>
       </c>
       <c r="O49" t="n">
-        <v>8.06</v>
+        <v>3.67</v>
       </c>
       <c r="P49" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.74</v>
+        <v>1.21</v>
       </c>
       <c r="R49" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>101.95</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="T49" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="U49" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="50">
@@ -3822,22 +3822,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>170.94</v>
+        <v>174.5</v>
       </c>
       <c r="D50" t="n">
-        <v>57.62</v>
+        <v>60.69</v>
       </c>
       <c r="E50" t="n">
-        <v>57.49</v>
+        <v>58.68</v>
       </c>
       <c r="F50" t="n">
-        <v>6.39</v>
+        <v>6.52</v>
       </c>
       <c r="G50" t="n">
-        <v>27644490000</v>
+        <v>28220220000</v>
       </c>
       <c r="H50" t="n">
-        <v>136.75</v>
+        <v>139.6</v>
       </c>
       <c r="I50" t="n">
         <v>194.67</v>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>13.88</v>
+        <v>11.56</v>
       </c>
       <c r="L50" t="n">
         <v>53.47</v>
@@ -3864,19 +3864,19 @@
         <v>0.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R50" t="n">
         <v>0.99</v>
       </c>
       <c r="S50" t="n">
-        <v>93.70999999999999</v>
+        <v>93.66</v>
       </c>
       <c r="T50" t="n">
         <v>1.53</v>
       </c>
       <c r="U50" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="51">
@@ -3891,22 +3891,22 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>409.64</v>
+        <v>419.79</v>
       </c>
       <c r="D51" t="n">
-        <v>53.88</v>
+        <v>57.76</v>
       </c>
       <c r="E51" t="n">
-        <v>40.05</v>
+        <v>41.04</v>
       </c>
       <c r="F51" t="n">
-        <v>5.58</v>
+        <v>5.72</v>
       </c>
       <c r="G51" t="n">
-        <v>159063210000</v>
+        <v>163004450000</v>
       </c>
       <c r="H51" t="n">
-        <v>327.71</v>
+        <v>335.83</v>
       </c>
       <c r="I51" t="n">
         <v>463.71</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>13.2</v>
+        <v>10.46</v>
       </c>
       <c r="L51" t="n">
         <v>16.84</v>
@@ -3933,7 +3933,7 @@
         <v>1.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R51" t="n">
         <v>0.2</v>
@@ -3945,7 +3945,7 @@
         <v>1.7</v>
       </c>
       <c r="U51" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="52">
@@ -3960,22 +3960,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>267.13</v>
+        <v>278.2</v>
       </c>
       <c r="D52" t="n">
-        <v>54.66</v>
+        <v>57.71</v>
       </c>
       <c r="E52" t="n">
-        <v>124.07</v>
+        <v>129.21</v>
       </c>
       <c r="F52" t="n">
-        <v>18.41</v>
+        <v>19.17</v>
       </c>
       <c r="G52" t="n">
-        <v>29853550000</v>
+        <v>31090270000</v>
       </c>
       <c r="H52" t="n">
-        <v>213.7</v>
+        <v>222.56</v>
       </c>
       <c r="I52" t="n">
         <v>313.83</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>17.48</v>
+        <v>12.81</v>
       </c>
       <c r="L52" t="n">
         <v>15.48</v>
@@ -4002,7 +4002,7 @@
         <v>0.05</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="R52" t="n">
         <v>6.3</v>
@@ -4014,7 +4014,7 @@
         <v>1.5</v>
       </c>
       <c r="U52" t="n">
-        <v>46.3</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="53">
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>374.18</v>
+        <v>394.1</v>
       </c>
       <c r="D53" t="n">
-        <v>65.59</v>
+        <v>69.5</v>
       </c>
       <c r="E53" t="n">
-        <v>70.63</v>
+        <v>74.39</v>
       </c>
       <c r="F53" t="n">
-        <v>21.58</v>
+        <v>22.73</v>
       </c>
       <c r="G53" t="n">
-        <v>467938670000</v>
+        <v>492850050000</v>
       </c>
       <c r="H53" t="n">
-        <v>299.34</v>
+        <v>315.28</v>
       </c>
       <c r="I53" t="n">
         <v>342</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>-8.6</v>
+        <v>-13.22</v>
       </c>
       <c r="L53" t="n">
         <v>23.76</v>
@@ -4071,19 +4071,19 @@
         <v>0.35</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R53" t="n">
         <v>0.34</v>
       </c>
       <c r="S53" t="n">
-        <v>84.52</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="T53" t="n">
         <v>1.57</v>
       </c>
       <c r="U53" t="n">
-        <v>45.4</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="54">
@@ -4098,25 +4098,25 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>115.21</v>
+        <v>118.94</v>
       </c>
       <c r="D54" t="n">
-        <v>56.26</v>
+        <v>58.75</v>
       </c>
       <c r="F54" t="n">
-        <v>10.09</v>
+        <v>10.42</v>
       </c>
       <c r="G54" t="n">
-        <v>62855160000</v>
+        <v>64890460000</v>
       </c>
       <c r="H54" t="n">
-        <v>92.17</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="I54" t="n">
         <v>138.91</v>
       </c>
       <c r="K54" t="n">
-        <v>20.57</v>
+        <v>16.79</v>
       </c>
       <c r="L54" t="n">
         <v>111.69</v>
@@ -4134,151 +4134,151 @@
         <v>7.39</v>
       </c>
       <c r="Q54" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="R54" t="n">
         <v>38.03</v>
       </c>
       <c r="S54" t="n">
-        <v>44.69</v>
+        <v>44.7</v>
       </c>
       <c r="T54" t="n">
         <v>1.92</v>
       </c>
       <c r="U54" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Land</t>
+          <t>AI Water</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>45.57</v>
+        <v>134.65</v>
       </c>
       <c r="D55" t="n">
-        <v>55.55</v>
+        <v>61.63</v>
+      </c>
+      <c r="E55" t="n">
+        <v>30.45</v>
       </c>
       <c r="F55" t="n">
-        <v>36.64</v>
+        <v>4.38</v>
       </c>
       <c r="G55" t="n">
-        <v>13022520000</v>
+        <v>3929840000</v>
       </c>
       <c r="H55" t="n">
-        <v>36.46</v>
+        <v>107.72</v>
       </c>
       <c r="I55" t="n">
-        <v>72.92</v>
+        <v>147</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>60.02</v>
+        <v>9.17</v>
       </c>
       <c r="L55" t="n">
-        <v>139.29</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>-120.39</v>
+        <v>-28.33</v>
       </c>
       <c r="N55" t="n">
-        <v>27.07</v>
+        <v>41.37</v>
       </c>
       <c r="O55" t="n">
-        <v>-54.12</v>
+        <v>14.56</v>
       </c>
       <c r="P55" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.65</v>
+        <v>0.65</v>
       </c>
       <c r="R55" t="n">
-        <v>9.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S55" t="n">
-        <v>70.27</v>
+        <v>108.1</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>2.13</v>
       </c>
       <c r="U55" t="n">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Land</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>592.92</v>
+        <v>47.15</v>
       </c>
       <c r="D56" t="n">
-        <v>73.38</v>
-      </c>
-      <c r="E56" t="n">
-        <v>55.71</v>
+        <v>58.11</v>
       </c>
       <c r="F56" t="n">
-        <v>16.22</v>
+        <v>37.91</v>
       </c>
       <c r="G56" t="n">
-        <v>470754400000</v>
+        <v>13474040000</v>
       </c>
       <c r="H56" t="n">
-        <v>474.34</v>
+        <v>37.72</v>
       </c>
       <c r="I56" t="n">
-        <v>529.8200000000001</v>
-      </c>
-      <c r="J56" t="b">
-        <v>0</v>
+        <v>72.92</v>
       </c>
       <c r="K56" t="n">
-        <v>-10.64</v>
+        <v>54.66</v>
       </c>
       <c r="L56" t="n">
-        <v>11.41</v>
+        <v>139.29</v>
       </c>
       <c r="M56" t="n">
-        <v>33.44</v>
+        <v>-120.39</v>
       </c>
       <c r="N56" t="n">
-        <v>48.96</v>
+        <v>27.07</v>
       </c>
       <c r="O56" t="n">
-        <v>29.31</v>
+        <v>-54.12</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3</v>
+        <v>1.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.63</v>
+        <v>5.64</v>
       </c>
       <c r="R56" t="n">
-        <v>0.46</v>
+        <v>9.48</v>
       </c>
       <c r="S56" t="n">
-        <v>81.87</v>
+        <v>70.28</v>
       </c>
       <c r="T56" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="57">
@@ -4293,22 +4293,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>294.03</v>
+        <v>300.5</v>
       </c>
       <c r="D57" t="n">
-        <v>53.82</v>
+        <v>56.18</v>
       </c>
       <c r="E57" t="n">
-        <v>57.46</v>
+        <v>58.73</v>
       </c>
       <c r="F57" t="n">
-        <v>9.460000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="G57" t="n">
-        <v>10711990000</v>
+        <v>10947710000</v>
       </c>
       <c r="H57" t="n">
-        <v>235.22</v>
+        <v>240.4</v>
       </c>
       <c r="I57" t="n">
         <v>289.17</v>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.65</v>
+        <v>-3.77</v>
       </c>
       <c r="L57" t="n">
         <v>6.45</v>
@@ -4341,82 +4341,82 @@
         <v>21.68</v>
       </c>
       <c r="S57" t="n">
-        <v>81.45999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="T57" t="n">
         <v>1.86</v>
       </c>
       <c r="U57" t="n">
-        <v>43.3</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Water</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>134.65</v>
+        <v>621.78</v>
       </c>
       <c r="D58" t="n">
-        <v>61.63</v>
+        <v>76.45</v>
       </c>
       <c r="E58" t="n">
-        <v>30.45</v>
+        <v>58.42</v>
       </c>
       <c r="F58" t="n">
-        <v>4.38</v>
+        <v>17.01</v>
       </c>
       <c r="G58" t="n">
-        <v>3929830000</v>
+        <v>493668110000</v>
       </c>
       <c r="H58" t="n">
-        <v>107.72</v>
+        <v>497.42</v>
       </c>
       <c r="I58" t="n">
-        <v>147</v>
+        <v>534.67</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>9.17</v>
+        <v>-14.01</v>
       </c>
       <c r="L58" t="n">
-        <v>-8.970000000000001</v>
+        <v>11.41</v>
       </c>
       <c r="M58" t="n">
-        <v>-28.33</v>
+        <v>33.44</v>
       </c>
       <c r="N58" t="n">
-        <v>41.37</v>
+        <v>48.96</v>
       </c>
       <c r="O58" t="n">
-        <v>14.56</v>
+        <v>29.31</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.66</v>
+        <v>1.58</v>
       </c>
       <c r="R58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="S58" t="n">
-        <v>108.11</v>
+        <v>81.87</v>
       </c>
       <c r="T58" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="U58" t="n">
-        <v>43.1</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="59">
@@ -4431,22 +4431,22 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1066.07</v>
+        <v>1114.55</v>
       </c>
       <c r="D59" t="n">
-        <v>73.8</v>
+        <v>76.48</v>
       </c>
       <c r="E59" t="n">
-        <v>101.19</v>
+        <v>105.79</v>
       </c>
       <c r="F59" t="n">
-        <v>21.71</v>
+        <v>22.7</v>
       </c>
       <c r="G59" t="n">
-        <v>239043790000</v>
+        <v>249913860000</v>
       </c>
       <c r="H59" t="n">
-        <v>852.86</v>
+        <v>891.64</v>
       </c>
       <c r="I59" t="n">
         <v>903.55</v>
@@ -4455,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.24</v>
+        <v>-18.93</v>
       </c>
       <c r="L59" t="n">
         <v>44.07</v>
@@ -4473,7 +4473,7 @@
         <v>3.82</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R59" t="n">
         <v>0.27</v>
@@ -4485,7 +4485,7 @@
         <v>1.59</v>
       </c>
       <c r="U59" t="n">
-        <v>43</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="60">
@@ -4500,22 +4500,22 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1088.52</v>
+        <v>1094</v>
       </c>
       <c r="D60" t="n">
-        <v>57.24</v>
+        <v>58.81</v>
       </c>
       <c r="E60" t="n">
-        <v>75.28</v>
+        <v>75.66</v>
       </c>
       <c r="F60" t="n">
-        <v>11.38</v>
+        <v>11.43</v>
       </c>
       <c r="G60" t="n">
-        <v>107354470000</v>
+        <v>107894930000</v>
       </c>
       <c r="H60" t="n">
-        <v>870.8200000000001</v>
+        <v>875.2</v>
       </c>
       <c r="I60" t="n">
         <v>1204.61</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>10.66</v>
+        <v>10.11</v>
       </c>
       <c r="L60" t="n">
         <v>9.84</v>
@@ -4554,7 +4554,7 @@
         <v>1.48</v>
       </c>
       <c r="U60" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="61">
@@ -4569,22 +4569,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>282.13</v>
+        <v>280.9</v>
       </c>
       <c r="D61" t="n">
-        <v>64.28</v>
+        <v>63.38</v>
       </c>
       <c r="E61" t="n">
-        <v>232.07</v>
+        <v>231.06</v>
       </c>
       <c r="F61" t="n">
-        <v>21.68</v>
+        <v>21.58</v>
       </c>
       <c r="G61" t="n">
-        <v>229935960000</v>
+        <v>228933490000</v>
       </c>
       <c r="H61" t="n">
-        <v>225.7</v>
+        <v>224.72</v>
       </c>
       <c r="I61" t="n">
         <v>320.25</v>
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>13.51</v>
+        <v>14.01</v>
       </c>
       <c r="L61" t="n">
         <v>31.15</v>
@@ -4611,19 +4611,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R61" t="n">
         <v>1.02</v>
       </c>
       <c r="S61" t="n">
-        <v>79.20999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="T61" t="n">
         <v>1.54</v>
       </c>
       <c r="U61" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="62">
@@ -4638,25 +4638,25 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7.66</v>
+        <v>7.79</v>
       </c>
       <c r="D62" t="n">
-        <v>66.88</v>
+        <v>67.73</v>
       </c>
       <c r="F62" t="n">
-        <v>234.71</v>
+        <v>238.69</v>
       </c>
       <c r="G62" t="n">
-        <v>1365990000</v>
+        <v>1389170000</v>
       </c>
       <c r="H62" t="n">
-        <v>6.13</v>
+        <v>6.23</v>
       </c>
       <c r="I62" t="n">
         <v>7</v>
       </c>
       <c r="K62" t="n">
-        <v>-8.619999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="L62" t="n">
         <v>479.14</v>
@@ -4674,7 +4674,7 @@
         <v>0.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="R62" t="n">
         <v>32.13</v>
@@ -4686,208 +4686,208 @@
         <v>1.67</v>
       </c>
       <c r="U62" t="n">
-        <v>41</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Backup Power</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>238.73</v>
+        <v>24</v>
       </c>
       <c r="D63" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="E63" t="n">
-        <v>67.48999999999999</v>
+        <v>54.95</v>
       </c>
       <c r="F63" t="n">
-        <v>23.82</v>
+        <v>1.71</v>
       </c>
       <c r="G63" t="n">
-        <v>311847090000</v>
+        <v>4423460000</v>
       </c>
       <c r="H63" t="n">
-        <v>190.98</v>
+        <v>19.2</v>
       </c>
       <c r="I63" t="n">
-        <v>200</v>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
+        <v>18.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.22</v>
+        <v>-22.29</v>
       </c>
       <c r="L63" t="n">
-        <v>11.52</v>
+        <v>7.71</v>
       </c>
       <c r="M63" t="n">
-        <v>11.65</v>
+        <v>33.88</v>
       </c>
       <c r="N63" t="n">
-        <v>59.91</v>
+        <v>11.1</v>
       </c>
       <c r="O63" t="n">
-        <v>35.68</v>
+        <v>-1.62</v>
       </c>
       <c r="P63" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.47</v>
+        <v>2.69</v>
       </c>
       <c r="R63" t="n">
-        <v>0.13</v>
+        <v>24.52</v>
       </c>
       <c r="S63" t="n">
-        <v>90.59999999999999</v>
+        <v>72.37</v>
       </c>
       <c r="T63" t="n">
-        <v>2.03</v>
+        <v>2.86</v>
       </c>
       <c r="U63" t="n">
-        <v>40.8</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Backup Power</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23.42</v>
+        <v>250.5</v>
       </c>
       <c r="D64" t="n">
-        <v>53.58</v>
+        <v>67.84</v>
+      </c>
+      <c r="E64" t="n">
+        <v>70.81999999999999</v>
       </c>
       <c r="F64" t="n">
-        <v>1.67</v>
+        <v>25</v>
       </c>
       <c r="G64" t="n">
-        <v>4316550000</v>
+        <v>327221960000</v>
       </c>
       <c r="H64" t="n">
-        <v>18.74</v>
+        <v>200.4</v>
       </c>
       <c r="I64" t="n">
-        <v>18.65</v>
+        <v>203.34</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.37</v>
+        <v>-18.83</v>
       </c>
       <c r="L64" t="n">
-        <v>7.71</v>
+        <v>11.52</v>
       </c>
       <c r="M64" t="n">
-        <v>33.88</v>
+        <v>11.65</v>
       </c>
       <c r="N64" t="n">
-        <v>11.1</v>
+        <v>59.91</v>
       </c>
       <c r="O64" t="n">
-        <v>-1.62</v>
+        <v>35.68</v>
       </c>
       <c r="P64" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.72</v>
+        <v>1.44</v>
       </c>
       <c r="R64" t="n">
-        <v>24.52</v>
+        <v>0.13</v>
       </c>
       <c r="S64" t="n">
-        <v>72.37</v>
+        <v>90.58</v>
       </c>
       <c r="T64" t="n">
-        <v>2.86</v>
+        <v>2.03</v>
       </c>
       <c r="U64" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Semiconductor Chip Manufacturing</t>
+          <t>AI Fire Detection</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>318.92</v>
+        <v>71</v>
       </c>
       <c r="D65" t="n">
-        <v>62.02</v>
+        <v>60.79</v>
       </c>
       <c r="E65" t="n">
-        <v>148.05</v>
+        <v>46.65</v>
       </c>
       <c r="F65" t="n">
-        <v>15.39</v>
+        <v>2.7</v>
       </c>
       <c r="G65" t="n">
-        <v>15864220000</v>
+        <v>58971290000</v>
       </c>
       <c r="H65" t="n">
-        <v>255.14</v>
+        <v>56.8</v>
       </c>
       <c r="I65" t="n">
-        <v>353.27</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>10.77</v>
+        <v>7.61</v>
       </c>
       <c r="L65" t="n">
-        <v>9.51</v>
+        <v>2.36</v>
       </c>
       <c r="M65" t="n">
-        <v>-47.97</v>
+        <v>-39.54</v>
       </c>
       <c r="N65" t="n">
-        <v>49.26</v>
+        <v>25.18</v>
       </c>
       <c r="O65" t="n">
-        <v>10.33</v>
+        <v>5.98</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="R65" t="n">
-        <v>0.63</v>
+        <v>4.74</v>
       </c>
       <c r="S65" t="n">
-        <v>99.22</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="T65" t="n">
-        <v>1.08</v>
+        <v>2.03</v>
       </c>
       <c r="U65" t="n">
-        <v>39.6</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="66">
@@ -4898,65 +4898,65 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>69.48999999999999</v>
+        <v>228.61</v>
       </c>
       <c r="D66" t="n">
-        <v>57.29</v>
+        <v>55.88</v>
       </c>
       <c r="E66" t="n">
-        <v>45.65</v>
+        <v>32.41</v>
       </c>
       <c r="F66" t="n">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="G66" t="n">
-        <v>57717030000</v>
+        <v>144859440000</v>
       </c>
       <c r="H66" t="n">
-        <v>55.59</v>
+        <v>182.89</v>
       </c>
       <c r="I66" t="n">
-        <v>76.40000000000001</v>
+        <v>251.87</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>9.94</v>
+        <v>10.17</v>
       </c>
       <c r="L66" t="n">
-        <v>2.36</v>
+        <v>-6.9</v>
       </c>
       <c r="M66" t="n">
-        <v>-39.54</v>
+        <v>-42.16</v>
       </c>
       <c r="N66" t="n">
-        <v>25.18</v>
+        <v>38.06</v>
       </c>
       <c r="O66" t="n">
-        <v>5.98</v>
+        <v>11.37</v>
       </c>
       <c r="P66" t="n">
-        <v>0.93</v>
+        <v>2.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.32</v>
+        <v>0.85</v>
       </c>
       <c r="R66" t="n">
-        <v>4.74</v>
+        <v>0.1</v>
       </c>
       <c r="S66" t="n">
-        <v>88.58</v>
+        <v>78.47</v>
       </c>
       <c r="T66" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>39.6</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="67">
@@ -4967,65 +4967,65 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>ONTO</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>175.45</v>
+        <v>335.6</v>
       </c>
       <c r="D67" t="n">
-        <v>58.52</v>
+        <v>65.98</v>
       </c>
       <c r="E67" t="n">
-        <v>54.66</v>
+        <v>155.8</v>
       </c>
       <c r="F67" t="n">
-        <v>6.38</v>
+        <v>16.2</v>
       </c>
       <c r="G67" t="n">
-        <v>5392110000</v>
+        <v>16693939999</v>
       </c>
       <c r="H67" t="n">
-        <v>140.36</v>
+        <v>268.48</v>
       </c>
       <c r="I67" t="n">
-        <v>161</v>
+        <v>353.27</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>-8.24</v>
+        <v>5.27</v>
       </c>
       <c r="L67" t="n">
-        <v>3.32</v>
+        <v>9.51</v>
       </c>
       <c r="M67" t="n">
-        <v>-66.34999999999999</v>
+        <v>-47.97</v>
       </c>
       <c r="N67" t="n">
-        <v>43.07</v>
+        <v>49.26</v>
       </c>
       <c r="O67" t="n">
-        <v>11.93</v>
+        <v>10.33</v>
       </c>
       <c r="P67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.89</v>
+        <v>1.56</v>
       </c>
       <c r="R67" t="n">
-        <v>1.43</v>
+        <v>0.63</v>
       </c>
       <c r="S67" t="n">
-        <v>111.62</v>
+        <v>99.22</v>
       </c>
       <c r="T67" t="n">
-        <v>2.67</v>
+        <v>1.08</v>
       </c>
       <c r="U67" t="n">
-        <v>38.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="68">
@@ -5036,134 +5036,134 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>80.64</v>
+        <v>182.12</v>
       </c>
       <c r="D68" t="n">
-        <v>55.21</v>
+        <v>61.37</v>
       </c>
       <c r="E68" t="n">
-        <v>57.93</v>
+        <v>56.74</v>
       </c>
       <c r="F68" t="n">
-        <v>6.47</v>
+        <v>6.62</v>
       </c>
       <c r="G68" t="n">
-        <v>44224300000</v>
+        <v>5597260000</v>
       </c>
       <c r="H68" t="n">
-        <v>64.51000000000001</v>
+        <v>145.7</v>
       </c>
       <c r="I68" t="n">
-        <v>80.7</v>
+        <v>161</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
       </c>
       <c r="K68" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-66.34999999999999</v>
+      </c>
+      <c r="N68" t="n">
+        <v>43.07</v>
+      </c>
+      <c r="O68" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="P68" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L68" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="M68" t="n">
-        <v>-51.3</v>
-      </c>
-      <c r="N68" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="O68" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0.15</v>
-      </c>
       <c r="Q68" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="R68" t="n">
-        <v>76.16</v>
+        <v>1.43</v>
       </c>
       <c r="S68" t="n">
-        <v>25.64</v>
+        <v>111.62</v>
       </c>
       <c r="T68" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="U68" t="n">
-        <v>38.6</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Fire Detection</t>
+          <t>AI Semiconductor Chip Manufacturing</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>228.61</v>
+        <v>83.25</v>
       </c>
       <c r="D69" t="n">
-        <v>55.88</v>
+        <v>58.24</v>
       </c>
       <c r="E69" t="n">
-        <v>32.41</v>
+        <v>59.81</v>
       </c>
       <c r="F69" t="n">
-        <v>3.65</v>
+        <v>6.67</v>
       </c>
       <c r="G69" t="n">
-        <v>144859440000</v>
+        <v>45655670000</v>
       </c>
       <c r="H69" t="n">
-        <v>182.89</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>251.87</v>
+        <v>80.7</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>10.17</v>
+        <v>-3.06</v>
       </c>
       <c r="L69" t="n">
-        <v>-6.9</v>
+        <v>3.09</v>
       </c>
       <c r="M69" t="n">
-        <v>-42.16</v>
+        <v>-51.3</v>
       </c>
       <c r="N69" t="n">
-        <v>38.06</v>
+        <v>26.11</v>
       </c>
       <c r="O69" t="n">
         <v>11.37</v>
       </c>
       <c r="P69" t="n">
-        <v>2.78</v>
+        <v>0.15</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.85</v>
+        <v>1.76</v>
       </c>
       <c r="R69" t="n">
-        <v>0.1</v>
+        <v>76.16</v>
       </c>
       <c r="S69" t="n">
-        <v>78.48</v>
+        <v>25.64</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U69" t="n">
-        <v>38.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="70">
@@ -5178,31 +5178,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>289.54</v>
+        <v>307</v>
       </c>
       <c r="D70" t="n">
-        <v>61.16</v>
+        <v>64.02</v>
       </c>
       <c r="E70" t="n">
-        <v>98.94</v>
+        <v>104.91</v>
       </c>
       <c r="F70" t="n">
-        <v>29.06</v>
+        <v>30.81</v>
       </c>
       <c r="G70" t="n">
-        <v>253289590000</v>
+        <v>268563599999</v>
       </c>
       <c r="H70" t="n">
-        <v>231.63</v>
+        <v>245.6</v>
       </c>
       <c r="I70" t="n">
-        <v>244.35</v>
+        <v>247.55</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-15.61</v>
+        <v>-19.36</v>
       </c>
       <c r="L70" t="n">
         <v>27.57</v>
@@ -5220,19 +5220,19 @@
         <v>0.3</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R70" t="n">
         <v>0.77</v>
       </c>
       <c r="S70" t="n">
-        <v>78.14</v>
+        <v>78.13</v>
       </c>
       <c r="T70" t="n">
         <v>1.43</v>
       </c>
       <c r="U70" t="n">
-        <v>37.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="71">
@@ -5247,25 +5247,25 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>121.1</v>
+        <v>132.59</v>
       </c>
       <c r="D71" t="n">
-        <v>57.34</v>
+        <v>63.57</v>
       </c>
       <c r="F71" t="n">
-        <v>11.32</v>
+        <v>12.4</v>
       </c>
       <c r="G71" t="n">
-        <v>608648600000</v>
+        <v>666421480000</v>
       </c>
       <c r="H71" t="n">
-        <v>96.88</v>
+        <v>106.07</v>
       </c>
       <c r="I71" t="n">
         <v>100.81</v>
       </c>
       <c r="K71" t="n">
-        <v>-16.75</v>
+        <v>-23.97</v>
       </c>
       <c r="L71" t="n">
         <v>7.18</v>
@@ -5283,7 +5283,7 @@
         <v>0.4</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R71" t="n">
         <v>15.51</v>
@@ -5295,7 +5295,7 @@
         <v>2.53</v>
       </c>
       <c r="U71" t="n">
-        <v>34.5</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="72">
@@ -5310,25 +5310,25 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10.29</v>
+        <v>10.3</v>
       </c>
       <c r="D72" t="n">
-        <v>50.36</v>
+        <v>50.48</v>
       </c>
       <c r="F72" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="G72" t="n">
-        <v>1495040000</v>
+        <v>1496440000</v>
       </c>
       <c r="H72" t="n">
-        <v>8.23</v>
+        <v>8.24</v>
       </c>
       <c r="I72" t="n">
         <v>8.82</v>
       </c>
       <c r="K72" t="n">
-        <v>-14.29</v>
+        <v>-14.37</v>
       </c>
       <c r="L72" t="n">
         <v>-52.54</v>
@@ -5346,7 +5346,7 @@
         <v>0.01</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="R72" t="n">
         <v>12.61</v>
@@ -5373,25 +5373,25 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>10.34</v>
+        <v>10.62</v>
       </c>
       <c r="D73" t="n">
-        <v>45.27</v>
+        <v>47.12</v>
       </c>
       <c r="F73" t="n">
-        <v>202.41</v>
+        <v>207.87</v>
       </c>
       <c r="G73" t="n">
-        <v>3779080000</v>
+        <v>3880940000</v>
       </c>
       <c r="H73" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="I73" t="n">
         <v>15.64</v>
       </c>
       <c r="K73" t="n">
-        <v>51.26</v>
+        <v>47.27</v>
       </c>
       <c r="L73" t="n">
         <v>-95.78</v>
@@ -5409,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R73" t="n">
         <v>3.08</v>
@@ -5421,7 +5421,7 @@
         <v>2.4</v>
       </c>
       <c r="U73" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
     </row>
   </sheetData>
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1931.77</v>
+        <v>1965</v>
       </c>
       <c r="C2" t="n">
-        <v>56.13</v>
+        <v>58.36</v>
       </c>
       <c r="D2" t="n">
-        <v>55.76</v>
+        <v>56.72</v>
       </c>
       <c r="E2" t="n">
-        <v>6.71</v>
+        <v>6.82</v>
       </c>
       <c r="F2" t="n">
-        <v>68002990000</v>
+        <v>69172770000</v>
       </c>
       <c r="G2" t="n">
-        <v>1545.42</v>
+        <v>1572</v>
       </c>
       <c r="H2" t="n">
         <v>2115.29</v>
@@ -5571,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9.5</v>
+        <v>7.65</v>
       </c>
       <c r="K2" t="n">
         <v>56.47</v>
@@ -5589,7 +5589,7 @@
         <v>0.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q2" t="n">
         <v>1.24</v>
@@ -5601,7 +5601,7 @@
         <v>1.45</v>
       </c>
       <c r="T2" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="3">
@@ -5611,22 +5611,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>827.5</v>
+        <v>835.75</v>
       </c>
       <c r="C3" t="n">
-        <v>46.79</v>
+        <v>49.01</v>
       </c>
       <c r="D3" t="n">
-        <v>27.69</v>
+        <v>27.97</v>
       </c>
       <c r="E3" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="F3" t="n">
-        <v>36774330000</v>
+        <v>37140960000</v>
       </c>
       <c r="G3" t="n">
-        <v>662</v>
+        <v>668.6</v>
       </c>
       <c r="H3" t="n">
         <v>1000.14</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20.86</v>
+        <v>19.67</v>
       </c>
       <c r="K3" t="n">
         <v>19.67</v>
@@ -5653,7 +5653,7 @@
         <v>0.13</v>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q3" t="n">
         <v>0.74</v>
@@ -5665,7 +5665,7 @@
         <v>1.91</v>
       </c>
       <c r="T3" t="n">
-        <v>52.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="4">
@@ -5675,22 +5675,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>838.21</v>
+        <v>856.5</v>
       </c>
       <c r="C4" t="n">
-        <v>53.18</v>
+        <v>54.94</v>
       </c>
       <c r="D4" t="n">
-        <v>74.94</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>8.92</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>25721270000</v>
+        <v>26282520000</v>
       </c>
       <c r="G4" t="n">
-        <v>670.5700000000001</v>
+        <v>685.2</v>
       </c>
       <c r="H4" t="n">
         <v>956.4299999999999</v>
@@ -5699,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>14.1</v>
+        <v>11.67</v>
       </c>
       <c r="K4" t="n">
         <v>91.59</v>
@@ -5723,13 +5723,13 @@
         <v>2.43</v>
       </c>
       <c r="R4" t="n">
-        <v>93.26000000000001</v>
+        <v>93.25</v>
       </c>
       <c r="S4" t="n">
         <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>61.5</v>
+        <v>60.9</v>
       </c>
     </row>
   </sheetData>
@@ -5855,25 +5855,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>682.96</v>
+        <v>679.99</v>
       </c>
       <c r="C2" t="n">
-        <v>57.83</v>
+        <v>57.12</v>
       </c>
       <c r="E2" t="n">
-        <v>34.13</v>
+        <v>33.98</v>
       </c>
       <c r="F2" t="n">
-        <v>173857600000</v>
+        <v>173101520000</v>
       </c>
       <c r="G2" t="n">
-        <v>546.37</v>
+        <v>543.99</v>
       </c>
       <c r="H2" t="n">
         <v>720.9299999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>5.56</v>
+        <v>6.02</v>
       </c>
       <c r="K2" t="n">
         <v>25.57</v>
@@ -5897,13 +5897,13 @@
         <v>3.56</v>
       </c>
       <c r="R2" t="n">
-        <v>71.22</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>1.59</v>
       </c>
       <c r="T2" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="3">
@@ -5913,22 +5913,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>282.13</v>
+        <v>280.9</v>
       </c>
       <c r="C3" t="n">
-        <v>64.28</v>
+        <v>63.38</v>
       </c>
       <c r="D3" t="n">
-        <v>232.07</v>
+        <v>231.06</v>
       </c>
       <c r="E3" t="n">
-        <v>21.68</v>
+        <v>21.58</v>
       </c>
       <c r="F3" t="n">
-        <v>229935960000</v>
+        <v>228933490000</v>
       </c>
       <c r="G3" t="n">
-        <v>225.7</v>
+        <v>224.72</v>
       </c>
       <c r="H3" t="n">
         <v>320.25</v>
@@ -5937,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>13.51</v>
+        <v>14.01</v>
       </c>
       <c r="K3" t="n">
         <v>31.15</v>
@@ -5955,19 +5955,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q3" t="n">
         <v>1.02</v>
       </c>
       <c r="R3" t="n">
-        <v>79.20999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="S3" t="n">
         <v>1.54</v>
       </c>
       <c r="T3" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="4">
@@ -5977,25 +5977,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>124.38</v>
+        <v>123.25</v>
       </c>
       <c r="C4" t="n">
-        <v>40.13</v>
+        <v>39.5</v>
       </c>
       <c r="E4" t="n">
-        <v>6.34</v>
+        <v>6.28</v>
       </c>
       <c r="F4" t="n">
-        <v>20113430000</v>
+        <v>19930700000</v>
       </c>
       <c r="G4" t="n">
-        <v>99.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>192.67</v>
       </c>
       <c r="J4" t="n">
-        <v>54.9</v>
+        <v>56.32</v>
       </c>
       <c r="K4" t="n">
         <v>25.43</v>
@@ -6013,19 +6013,19 @@
         <v>0.79</v>
       </c>
       <c r="P4" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="Q4" t="n">
         <v>35.18</v>
       </c>
       <c r="R4" t="n">
-        <v>54.2</v>
+        <v>54.19</v>
       </c>
       <c r="S4" t="n">
         <v>1.48</v>
       </c>
       <c r="T4" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>113.03</v>
+        <v>111.64</v>
       </c>
       <c r="C5" t="n">
-        <v>55.91</v>
+        <v>54.46</v>
       </c>
       <c r="D5" t="n">
-        <v>82.09999999999999</v>
+        <v>81.09</v>
       </c>
       <c r="E5" t="n">
-        <v>6.56</v>
+        <v>6.48</v>
       </c>
       <c r="F5" t="n">
-        <v>19645440000</v>
+        <v>19403860000</v>
       </c>
       <c r="G5" t="n">
-        <v>90.42</v>
+        <v>89.31</v>
       </c>
       <c r="H5" t="n">
         <v>120.2</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>6.34</v>
+        <v>7.67</v>
       </c>
       <c r="K5" t="n">
         <v>11.19</v>
@@ -6077,7 +6077,7 @@
         <v>0.06</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Q5" t="n">
         <v>4.97</v>
@@ -6089,7 +6089,7 @@
         <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="6">
@@ -6099,25 +6099,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.23999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>50.41</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>14251550000</v>
+        <v>14191450000</v>
       </c>
       <c r="G6" t="n">
-        <v>55.39</v>
+        <v>55.16</v>
       </c>
       <c r="H6" t="n">
         <v>94.37</v>
       </c>
       <c r="J6" t="n">
-        <v>36.29</v>
+        <v>36.87</v>
       </c>
       <c r="K6" t="n">
         <v>38.99</v>
@@ -6132,19 +6132,19 @@
         <v>-20.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>26.66</v>
       </c>
       <c r="R6" t="n">
-        <v>57.43</v>
+        <v>57.42</v>
       </c>
       <c r="S6" t="n">
         <v>1.1</v>
       </c>
       <c r="T6" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
@@ -6270,31 +6270,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>592.92</v>
+        <v>621.78</v>
       </c>
       <c r="C2" t="n">
-        <v>73.38</v>
+        <v>76.45</v>
       </c>
       <c r="D2" t="n">
-        <v>55.71</v>
+        <v>58.42</v>
       </c>
       <c r="E2" t="n">
-        <v>16.22</v>
+        <v>17.01</v>
       </c>
       <c r="F2" t="n">
-        <v>470754400000</v>
+        <v>493668110000</v>
       </c>
       <c r="G2" t="n">
-        <v>474.34</v>
+        <v>497.42</v>
       </c>
       <c r="H2" t="n">
-        <v>529.8200000000001</v>
+        <v>534.67</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-10.64</v>
+        <v>-14.01</v>
       </c>
       <c r="K2" t="n">
         <v>11.41</v>
@@ -6312,7 +6312,7 @@
         <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>0.46</v>
@@ -6324,7 +6324,7 @@
         <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>43.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="3">
@@ -6334,22 +6334,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>374.18</v>
+        <v>394.1</v>
       </c>
       <c r="C3" t="n">
-        <v>65.59</v>
+        <v>69.5</v>
       </c>
       <c r="D3" t="n">
-        <v>70.63</v>
+        <v>74.39</v>
       </c>
       <c r="E3" t="n">
-        <v>21.58</v>
+        <v>22.73</v>
       </c>
       <c r="F3" t="n">
-        <v>467938670000</v>
+        <v>492850050000</v>
       </c>
       <c r="G3" t="n">
-        <v>299.34</v>
+        <v>315.28</v>
       </c>
       <c r="H3" t="n">
         <v>342</v>
@@ -6358,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-8.6</v>
+        <v>-13.22</v>
       </c>
       <c r="K3" t="n">
         <v>23.76</v>
@@ -6376,19 +6376,19 @@
         <v>0.35</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q3" t="n">
         <v>0.34</v>
       </c>
       <c r="R3" t="n">
-        <v>84.52</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="S3" t="n">
         <v>1.57</v>
       </c>
       <c r="T3" t="n">
-        <v>45.4</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="4">
@@ -6398,31 +6398,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238.73</v>
+        <v>250.5</v>
       </c>
       <c r="C4" t="n">
-        <v>64.15000000000001</v>
+        <v>67.84</v>
       </c>
       <c r="D4" t="n">
-        <v>67.48999999999999</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>23.82</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>311847090000</v>
+        <v>327221960000</v>
       </c>
       <c r="G4" t="n">
-        <v>190.98</v>
+        <v>200.4</v>
       </c>
       <c r="H4" t="n">
-        <v>200</v>
+        <v>203.34</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-16.22</v>
+        <v>-18.83</v>
       </c>
       <c r="K4" t="n">
         <v>11.52</v>
@@ -6440,19 +6440,19 @@
         <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q4" t="n">
         <v>0.13</v>
       </c>
       <c r="R4" t="n">
-        <v>90.59999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="S4" t="n">
         <v>2.03</v>
       </c>
       <c r="T4" t="n">
-        <v>40.8</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="5">
@@ -6462,22 +6462,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>318.92</v>
+        <v>335.6</v>
       </c>
       <c r="C5" t="n">
-        <v>62.02</v>
+        <v>65.98</v>
       </c>
       <c r="D5" t="n">
-        <v>148.05</v>
+        <v>155.8</v>
       </c>
       <c r="E5" t="n">
-        <v>15.39</v>
+        <v>16.2</v>
       </c>
       <c r="F5" t="n">
-        <v>15864220000</v>
+        <v>16693939999</v>
       </c>
       <c r="G5" t="n">
-        <v>255.14</v>
+        <v>268.48</v>
       </c>
       <c r="H5" t="n">
         <v>353.27</v>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10.77</v>
+        <v>5.27</v>
       </c>
       <c r="K5" t="n">
         <v>9.51</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
         <v>0.63</v>
@@ -6516,7 +6516,7 @@
         <v>1.08</v>
       </c>
       <c r="T5" t="n">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="6">
@@ -6526,22 +6526,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>175.45</v>
+        <v>182.12</v>
       </c>
       <c r="C6" t="n">
-        <v>58.52</v>
+        <v>61.37</v>
       </c>
       <c r="D6" t="n">
-        <v>54.66</v>
+        <v>56.74</v>
       </c>
       <c r="E6" t="n">
-        <v>6.38</v>
+        <v>6.62</v>
       </c>
       <c r="F6" t="n">
-        <v>5392110000</v>
+        <v>5597260000</v>
       </c>
       <c r="G6" t="n">
-        <v>140.36</v>
+        <v>145.7</v>
       </c>
       <c r="H6" t="n">
         <v>161</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.24</v>
+        <v>-11.6</v>
       </c>
       <c r="K6" t="n">
         <v>3.32</v>
@@ -6568,7 +6568,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.43</v>
@@ -6580,7 +6580,7 @@
         <v>2.67</v>
       </c>
       <c r="T6" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="7">
@@ -6590,22 +6590,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.01</v>
+        <v>32.11</v>
       </c>
       <c r="C7" t="n">
-        <v>36.56</v>
+        <v>39.43</v>
       </c>
       <c r="D7" t="n">
-        <v>11.36</v>
+        <v>11.76</v>
       </c>
       <c r="E7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1828470000</v>
+        <v>1893320000</v>
       </c>
       <c r="G7" t="n">
-        <v>24.81</v>
+        <v>25.69</v>
       </c>
       <c r="H7" t="n">
         <v>43</v>
@@ -6614,7 +6614,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>38.66</v>
+        <v>33.91</v>
       </c>
       <c r="K7" t="n">
         <v>-0.5</v>
@@ -6644,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>63.7</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="8">
@@ -6654,22 +6654,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>432.15</v>
+        <v>438.75</v>
       </c>
       <c r="C8" t="n">
-        <v>55.24</v>
+        <v>57.34</v>
       </c>
       <c r="D8" t="n">
-        <v>35.92</v>
+        <v>36.46</v>
       </c>
       <c r="E8" t="n">
-        <v>16.87</v>
+        <v>17.13</v>
       </c>
       <c r="F8" t="n">
-        <v>2241337300000</v>
+        <v>2275557180000</v>
       </c>
       <c r="G8" t="n">
-        <v>345.72</v>
+        <v>351</v>
       </c>
       <c r="H8" t="n">
         <v>460.4</v>
@@ -6678,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>6.54</v>
+        <v>4.93</v>
       </c>
       <c r="K8" t="n">
         <v>40.49</v>
@@ -6696,19 +6696,19 @@
         <v>0.19</v>
       </c>
       <c r="P8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q8" t="n">
         <v>0.09</v>
       </c>
       <c r="R8" t="n">
-        <v>15.17</v>
+        <v>15.16</v>
       </c>
       <c r="S8" t="n">
         <v>1.21</v>
       </c>
       <c r="T8" t="n">
-        <v>59.3</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="9">
@@ -6718,22 +6718,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.64</v>
+        <v>83.25</v>
       </c>
       <c r="C9" t="n">
-        <v>55.21</v>
+        <v>58.24</v>
       </c>
       <c r="D9" t="n">
-        <v>57.93</v>
+        <v>59.81</v>
       </c>
       <c r="E9" t="n">
-        <v>6.47</v>
+        <v>6.67</v>
       </c>
       <c r="F9" t="n">
-        <v>44224300000</v>
+        <v>45655670000</v>
       </c>
       <c r="G9" t="n">
-        <v>64.51000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>80.7</v>
@@ -6742,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-3.06</v>
       </c>
       <c r="K9" t="n">
         <v>3.09</v>
@@ -6760,7 +6760,7 @@
         <v>0.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
         <v>76.16</v>
@@ -6772,7 +6772,7 @@
         <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>38.6</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="10">
@@ -6782,25 +6782,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121.1</v>
+        <v>132.59</v>
       </c>
       <c r="C10" t="n">
-        <v>57.34</v>
+        <v>63.57</v>
       </c>
       <c r="E10" t="n">
-        <v>11.32</v>
+        <v>12.4</v>
       </c>
       <c r="F10" t="n">
-        <v>608648600000</v>
+        <v>666421480000</v>
       </c>
       <c r="G10" t="n">
-        <v>96.88</v>
+        <v>106.07</v>
       </c>
       <c r="H10" t="n">
         <v>100.81</v>
       </c>
       <c r="J10" t="n">
-        <v>-16.75</v>
+        <v>-23.97</v>
       </c>
       <c r="K10" t="n">
         <v>7.18</v>
@@ -6818,7 +6818,7 @@
         <v>0.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
         <v>15.51</v>
@@ -6830,7 +6830,7 @@
         <v>2.53</v>
       </c>
       <c r="T10" t="n">
-        <v>34.5</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="11">
@@ -6840,22 +6840,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>267.13</v>
+        <v>278.2</v>
       </c>
       <c r="C11" t="n">
-        <v>54.66</v>
+        <v>57.71</v>
       </c>
       <c r="D11" t="n">
-        <v>124.07</v>
+        <v>129.21</v>
       </c>
       <c r="E11" t="n">
-        <v>18.41</v>
+        <v>19.17</v>
       </c>
       <c r="F11" t="n">
-        <v>29853550000</v>
+        <v>31090270000</v>
       </c>
       <c r="G11" t="n">
-        <v>213.7</v>
+        <v>222.56</v>
       </c>
       <c r="H11" t="n">
         <v>313.83</v>
@@ -6864,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>17.48</v>
+        <v>12.81</v>
       </c>
       <c r="K11" t="n">
         <v>15.48</v>
@@ -6882,7 +6882,7 @@
         <v>0.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="Q11" t="n">
         <v>6.3</v>
@@ -6894,7 +6894,7 @@
         <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>46.3</v>
+        <v>45.1</v>
       </c>
     </row>
   </sheetData>
@@ -7020,22 +7020,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.78</v>
+        <v>28.53</v>
       </c>
       <c r="C2" t="n">
-        <v>38.04</v>
+        <v>39.52</v>
       </c>
       <c r="D2" t="n">
-        <v>14.65</v>
+        <v>15.05</v>
       </c>
       <c r="E2" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="F2" t="n">
-        <v>17970130000</v>
+        <v>18455280000</v>
       </c>
       <c r="G2" t="n">
-        <v>22.22</v>
+        <v>22.82</v>
       </c>
       <c r="H2" t="n">
         <v>35.87</v>
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>29.12</v>
+        <v>25.73</v>
       </c>
       <c r="K2" t="n">
         <v>122.68</v>
@@ -7062,7 +7062,7 @@
         <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
         <v>13.87</v>
@@ -7074,7 +7074,7 @@
         <v>2.9</v>
       </c>
       <c r="T2" t="n">
-        <v>66.90000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="3">
@@ -7084,28 +7084,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>419.32</v>
+        <v>428</v>
       </c>
       <c r="C3" t="n">
-        <v>67.58</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>33.32</v>
+        <v>34.01</v>
       </c>
       <c r="E3" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="F3" t="n">
-        <v>271764640000</v>
+        <v>277390210000</v>
       </c>
       <c r="G3" t="n">
-        <v>335.46</v>
+        <v>342.4</v>
       </c>
       <c r="H3" t="n">
-        <v>496.76</v>
+        <v>499.86</v>
       </c>
       <c r="J3" t="n">
-        <v>18.47</v>
+        <v>16.79</v>
       </c>
       <c r="K3" t="n">
         <v>87.48999999999999</v>
@@ -7120,7 +7120,7 @@
         <v>6.27</v>
       </c>
       <c r="P3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
         <v>53.55</v>
@@ -7132,7 +7132,7 @@
         <v>1.73</v>
       </c>
       <c r="T3" t="n">
-        <v>59.4</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="4">
@@ -7142,22 +7142,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48.2</v>
+        <v>49.33</v>
       </c>
       <c r="C4" t="n">
-        <v>62.47</v>
+        <v>64.39</v>
       </c>
       <c r="D4" t="n">
-        <v>46.21</v>
+        <v>47.3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="F4" t="n">
-        <v>63826610000</v>
+        <v>65322960000</v>
       </c>
       <c r="G4" t="n">
-        <v>38.56</v>
+        <v>39.46</v>
       </c>
       <c r="H4" t="n">
         <v>68.59</v>
@@ -7166,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>42.3</v>
+        <v>39.04</v>
       </c>
       <c r="K4" t="n">
         <v>40.64</v>
@@ -7184,7 +7184,7 @@
         <v>0.84</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
         <v>0.38</v>
@@ -7196,7 +7196,7 @@
         <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>56.2</v>
+        <v>55.5</v>
       </c>
     </row>
   </sheetData>
@@ -7322,22 +7322,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.48</v>
+        <v>94.8</v>
       </c>
       <c r="C2" t="n">
-        <v>41.14</v>
+        <v>40.64</v>
       </c>
       <c r="D2" t="n">
-        <v>56.8</v>
+        <v>56.39</v>
       </c>
       <c r="E2" t="n">
-        <v>7.05</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>98469290000</v>
+        <v>97768000000</v>
       </c>
       <c r="G2" t="n">
-        <v>76.38</v>
+        <v>75.84</v>
       </c>
       <c r="H2" t="n">
         <v>140.76</v>
@@ -7346,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>47.42</v>
+        <v>48.48</v>
       </c>
       <c r="K2" t="n">
         <v>22.09</v>
@@ -7364,19 +7364,19 @@
         <v>0.21</v>
       </c>
       <c r="P2" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="Q2" t="n">
         <v>0.91</v>
       </c>
       <c r="R2" t="n">
-        <v>86.27</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>57.1</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="3">
@@ -7386,22 +7386,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>226.63</v>
+        <v>224.23</v>
       </c>
       <c r="C3" t="n">
-        <v>54.78</v>
+        <v>53.2</v>
       </c>
       <c r="D3" t="n">
-        <v>604.83</v>
+        <v>598.42</v>
       </c>
       <c r="E3" t="n">
-        <v>21.97</v>
+        <v>21.74</v>
       </c>
       <c r="F3" t="n">
-        <v>80671260000</v>
+        <v>79816140000</v>
       </c>
       <c r="G3" t="n">
-        <v>181.3</v>
+        <v>179.38</v>
       </c>
       <c r="H3" t="n">
         <v>242.39</v>
@@ -7410,7 +7410,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.95</v>
+        <v>8.1</v>
       </c>
       <c r="K3" t="n">
         <v>32.15</v>
@@ -7428,7 +7428,7 @@
         <v>0.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q3" t="n">
         <v>9.06</v>
@@ -7440,7 +7440,7 @@
         <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="4">
@@ -7450,31 +7450,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.25</v>
+        <v>40.92</v>
       </c>
       <c r="C4" t="n">
-        <v>52.98</v>
+        <v>51.34</v>
       </c>
       <c r="D4" t="n">
-        <v>76.94</v>
+        <v>76.33</v>
       </c>
       <c r="E4" t="n">
-        <v>5.96</v>
+        <v>5.91</v>
       </c>
       <c r="F4" t="n">
-        <v>12023370000</v>
+        <v>11927180000</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>32.74</v>
       </c>
       <c r="H4" t="n">
-        <v>45.25</v>
+        <v>45.41</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.97</v>
       </c>
       <c r="K4" t="n">
         <v>19.44</v>
@@ -7504,7 +7504,7 @@
         <v>1.77</v>
       </c>
       <c r="T4" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="5">
@@ -7514,25 +7514,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.29</v>
+        <v>10.3</v>
       </c>
       <c r="C5" t="n">
-        <v>50.36</v>
+        <v>50.48</v>
       </c>
       <c r="E5" t="n">
-        <v>5.97</v>
+        <v>5.98</v>
       </c>
       <c r="F5" t="n">
-        <v>1495040000</v>
+        <v>1496440000</v>
       </c>
       <c r="G5" t="n">
-        <v>8.23</v>
+        <v>8.24</v>
       </c>
       <c r="H5" t="n">
         <v>8.82</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.29</v>
+        <v>-14.37</v>
       </c>
       <c r="K5" t="n">
         <v>-52.54</v>
@@ -7550,7 +7550,7 @@
         <v>0.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
         <v>12.61</v>
@@ -7572,25 +7572,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>334.69</v>
+        <v>333.11</v>
       </c>
       <c r="C6" t="n">
-        <v>50.23</v>
+        <v>49.77</v>
       </c>
       <c r="E6" t="n">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="F6" t="n">
-        <v>26919760000</v>
+        <v>26792680000</v>
       </c>
       <c r="G6" t="n">
-        <v>267.75</v>
+        <v>266.49</v>
       </c>
       <c r="H6" t="n">
         <v>399.82</v>
       </c>
       <c r="J6" t="n">
-        <v>19.46</v>
+        <v>20.03</v>
       </c>
       <c r="K6" t="n">
         <v>25.25</v>
@@ -7617,10 +7617,10 @@
         <v>90.63</v>
       </c>
       <c r="S6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T6" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7746,25 +7746,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>284.99</v>
+        <v>296.64</v>
       </c>
       <c r="C2" t="n">
-        <v>55.12</v>
+        <v>58.22</v>
       </c>
       <c r="E2" t="n">
-        <v>33.1</v>
+        <v>34.45</v>
       </c>
       <c r="F2" t="n">
-        <v>81063660000</v>
+        <v>84377440000</v>
       </c>
       <c r="G2" t="n">
-        <v>227.99</v>
+        <v>237.31</v>
       </c>
       <c r="H2" t="n">
         <v>279.01</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.1</v>
+        <v>-5.94</v>
       </c>
       <c r="K2" t="n">
         <v>130.37</v>
@@ -7782,7 +7782,7 @@
         <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="Q2" t="n">
         <v>6.31</v>
@@ -7794,7 +7794,7 @@
         <v>2.26</v>
       </c>
       <c r="T2" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="3">
@@ -7804,25 +7804,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.42</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>53.58</v>
+        <v>54.95</v>
       </c>
       <c r="E3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="F3" t="n">
-        <v>4316550000</v>
+        <v>4423460000</v>
       </c>
       <c r="G3" t="n">
-        <v>18.74</v>
+        <v>19.2</v>
       </c>
       <c r="H3" t="n">
         <v>18.65</v>
       </c>
       <c r="J3" t="n">
-        <v>-20.37</v>
+        <v>-22.29</v>
       </c>
       <c r="K3" t="n">
         <v>7.71</v>
@@ -7840,7 +7840,7 @@
         <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="Q3" t="n">
         <v>24.52</v>
@@ -7852,7 +7852,7 @@
         <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>40.8</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="4">
@@ -7862,25 +7862,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.66</v>
+        <v>7.79</v>
       </c>
       <c r="C4" t="n">
-        <v>66.88</v>
+        <v>67.73</v>
       </c>
       <c r="E4" t="n">
-        <v>234.71</v>
+        <v>238.69</v>
       </c>
       <c r="F4" t="n">
-        <v>1365990000</v>
+        <v>1389170000</v>
       </c>
       <c r="G4" t="n">
-        <v>6.13</v>
+        <v>6.23</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.619999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="K4" t="n">
         <v>479.14</v>
@@ -7898,7 +7898,7 @@
         <v>0.02</v>
       </c>
       <c r="P4" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="Q4" t="n">
         <v>32.13</v>
@@ -7910,7 +7910,7 @@
         <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>41</v>
+        <v>40.7</v>
       </c>
     </row>
   </sheetData>
@@ -8036,22 +8036,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>378.91</v>
+        <v>377.5</v>
       </c>
       <c r="C2" t="n">
-        <v>34.59</v>
+        <v>34.11</v>
       </c>
       <c r="D2" t="n">
-        <v>22.57</v>
+        <v>22.48</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>8.81</v>
       </c>
       <c r="F2" t="n">
-        <v>2814708170000</v>
+        <v>2804234050000</v>
       </c>
       <c r="G2" t="n">
-        <v>303.13</v>
+        <v>302</v>
       </c>
       <c r="H2" t="n">
         <v>559.29</v>
@@ -8060,7 +8060,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>47.6</v>
+        <v>48.16</v>
       </c>
       <c r="K2" t="n">
         <v>18.3</v>
@@ -8078,19 +8078,19 @@
         <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Q2" t="n">
         <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>74.77</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="3">
@@ -8100,22 +8100,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>237.5</v>
+        <v>238.35</v>
       </c>
       <c r="C3" t="n">
-        <v>36.89</v>
+        <v>37.87</v>
       </c>
       <c r="D3" t="n">
-        <v>28.38</v>
+        <v>28.48</v>
       </c>
       <c r="E3" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="F3" t="n">
-        <v>2554813480000</v>
+        <v>2563957090000</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>190.68</v>
       </c>
       <c r="H3" t="n">
         <v>316.56</v>
@@ -8124,7 +8124,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>33.29</v>
+        <v>32.81</v>
       </c>
       <c r="K3" t="n">
         <v>16.61</v>
@@ -8142,7 +8142,7 @@
         <v>0.51</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q3" t="n">
         <v>8.949999999999999</v>
@@ -8154,7 +8154,7 @@
         <v>1.22</v>
       </c>
       <c r="T3" t="n">
-        <v>61.5</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="4">
@@ -8164,22 +8164,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>183.53</v>
+        <v>182.64</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62</v>
+        <v>42.22</v>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>31.35</v>
       </c>
       <c r="E4" t="n">
-        <v>7.84</v>
+        <v>7.8</v>
       </c>
       <c r="F4" t="n">
-        <v>527840699999</v>
+        <v>525281020000</v>
       </c>
       <c r="G4" t="n">
-        <v>146.82</v>
+        <v>146.11</v>
       </c>
       <c r="H4" t="n">
         <v>255.38</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>39.15</v>
+        <v>39.83</v>
       </c>
       <c r="K4" t="n">
         <v>20.63</v>
@@ -8206,7 +8206,7 @@
         <v>3.63</v>
       </c>
       <c r="P4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q4" t="n">
         <v>40.54</v>
@@ -8215,10 +8215,10 @@
         <v>43.83</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="5">
@@ -8228,25 +8228,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115.21</v>
+        <v>118.94</v>
       </c>
       <c r="C5" t="n">
-        <v>56.26</v>
+        <v>58.75</v>
       </c>
       <c r="E5" t="n">
-        <v>10.09</v>
+        <v>10.42</v>
       </c>
       <c r="F5" t="n">
-        <v>62855160000</v>
+        <v>64890460000</v>
       </c>
       <c r="G5" t="n">
-        <v>92.17</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>138.91</v>
       </c>
       <c r="J5" t="n">
-        <v>20.57</v>
+        <v>16.79</v>
       </c>
       <c r="K5" t="n">
         <v>111.69</v>
@@ -8264,19 +8264,19 @@
         <v>7.39</v>
       </c>
       <c r="P5" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Q5" t="n">
         <v>38.03</v>
       </c>
       <c r="R5" t="n">
-        <v>44.69</v>
+        <v>44.7</v>
       </c>
       <c r="S5" t="n">
         <v>1.92</v>
       </c>
       <c r="T5" t="n">
-        <v>44.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="6">
@@ -8286,22 +8286,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>280.91</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>68.56999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>93.72</v>
+        <v>98.09</v>
       </c>
       <c r="E6" t="n">
-        <v>80.52</v>
+        <v>84.28</v>
       </c>
       <c r="F6" t="n">
-        <v>70691120000</v>
+        <v>73985230000</v>
       </c>
       <c r="G6" t="n">
-        <v>224.73</v>
+        <v>235.2</v>
       </c>
       <c r="H6" t="n">
         <v>255.29</v>
@@ -8310,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.119999999999999</v>
+        <v>-13.17</v>
       </c>
       <c r="K6" t="n">
         <v>621.52</v>
@@ -8328,19 +8328,19 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="Q6" t="n">
         <v>19.73</v>
       </c>
       <c r="R6" t="n">
-        <v>50.26</v>
+        <v>50.29</v>
       </c>
       <c r="S6" t="n">
         <v>1.94</v>
       </c>
       <c r="T6" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="7">
@@ -8350,22 +8350,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>363.79</v>
+        <v>362.7</v>
       </c>
       <c r="C7" t="n">
-        <v>46.1</v>
+        <v>45.41</v>
       </c>
       <c r="D7" t="n">
-        <v>27.75</v>
+        <v>27.67</v>
       </c>
       <c r="E7" t="n">
-        <v>10.39</v>
+        <v>10.36</v>
       </c>
       <c r="F7" t="n">
-        <v>4396287980000</v>
+        <v>4385321639999</v>
       </c>
       <c r="G7" t="n">
-        <v>291.03</v>
+        <v>290.16</v>
       </c>
       <c r="H7" t="n">
         <v>433.97</v>
@@ -8374,7 +8374,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>19.29</v>
+        <v>19.65</v>
       </c>
       <c r="K7" t="n">
         <v>22.34</v>
@@ -8404,7 +8404,7 @@
         <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>63.1</v>
+        <v>63.3</v>
       </c>
     </row>
   </sheetData>
@@ -8530,22 +8530,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143.62</v>
+        <v>146.97</v>
       </c>
       <c r="C2" t="n">
-        <v>52.21</v>
+        <v>56.64</v>
       </c>
       <c r="D2" t="n">
-        <v>25.69</v>
+        <v>26.29</v>
       </c>
       <c r="E2" t="n">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="F2" t="n">
-        <v>87624800000</v>
+        <v>89668690000</v>
       </c>
       <c r="G2" t="n">
-        <v>114.9</v>
+        <v>117.58</v>
       </c>
       <c r="H2" t="n">
         <v>157.1</v>
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>9.390000000000001</v>
+        <v>6.89</v>
       </c>
       <c r="K2" t="n">
         <v>8.210000000000001</v>
@@ -8572,19 +8572,19 @@
         <v>0.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q2" t="n">
         <v>0.34</v>
       </c>
       <c r="R2" t="n">
-        <v>92.81999999999999</v>
+        <v>92.81</v>
       </c>
       <c r="S2" t="n">
         <v>2.19</v>
       </c>
       <c r="T2" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="3">
@@ -8594,22 +8594,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.48999999999999</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>57.29</v>
+        <v>60.79</v>
       </c>
       <c r="D3" t="n">
-        <v>45.65</v>
+        <v>46.65</v>
       </c>
       <c r="E3" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>57717030000</v>
+        <v>58971290000</v>
       </c>
       <c r="G3" t="n">
-        <v>55.59</v>
+        <v>56.8</v>
       </c>
       <c r="H3" t="n">
         <v>76.40000000000001</v>
@@ -8618,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>9.94</v>
+        <v>7.61</v>
       </c>
       <c r="K3" t="n">
         <v>2.36</v>
@@ -8636,19 +8636,19 @@
         <v>0.93</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q3" t="n">
         <v>4.74</v>
       </c>
       <c r="R3" t="n">
-        <v>88.58</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>2.03</v>
       </c>
       <c r="T3" t="n">
-        <v>39.6</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="4">
@@ -8706,7 +8706,7 @@
         <v>0.1</v>
       </c>
       <c r="R4" t="n">
-        <v>78.48</v>
+        <v>78.47</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -8838,22 +8838,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110.29</v>
+        <v>112.01</v>
       </c>
       <c r="C2" t="n">
-        <v>47.39</v>
+        <v>52.13</v>
       </c>
       <c r="D2" t="n">
-        <v>27.4</v>
+        <v>27.83</v>
       </c>
       <c r="E2" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="F2" t="n">
-        <v>26215210000</v>
+        <v>26624050000</v>
       </c>
       <c r="G2" t="n">
-        <v>88.23</v>
+        <v>89.61</v>
       </c>
       <c r="H2" t="n">
         <v>152.31</v>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>38.1</v>
+        <v>35.98</v>
       </c>
       <c r="K2" t="n">
         <v>2.71</v>
@@ -8886,13 +8886,13 @@
         <v>0.35</v>
       </c>
       <c r="R2" t="n">
-        <v>95.73999999999999</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>52.4</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="3">
@@ -8914,7 +8914,7 @@
         <v>4.38</v>
       </c>
       <c r="F3" t="n">
-        <v>3929830000</v>
+        <v>3929840000</v>
       </c>
       <c r="G3" t="n">
         <v>107.72</v>
@@ -8944,13 +8944,13 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="Q3" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>108.11</v>
+        <v>108.1</v>
       </c>
       <c r="S3" t="n">
         <v>2.13</v>
@@ -8966,22 +8966,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.65</v>
+        <v>25.74</v>
       </c>
       <c r="C4" t="n">
-        <v>47.42</v>
+        <v>48.53</v>
       </c>
       <c r="D4" t="n">
-        <v>19.46</v>
+        <v>19.53</v>
       </c>
       <c r="E4" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="F4" t="n">
-        <v>4013490000</v>
+        <v>4027560000</v>
       </c>
       <c r="G4" t="n">
-        <v>20.52</v>
+        <v>20.59</v>
       </c>
       <c r="H4" t="n">
         <v>32.2</v>
@@ -8990,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>25.54</v>
+        <v>25.1</v>
       </c>
       <c r="K4" t="n">
         <v>5.52</v>
@@ -9008,7 +9008,7 @@
         <v>0.42</v>
       </c>
       <c r="P4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9</v>
@@ -9020,7 +9020,7 @@
         <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>52.3</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -9164,13 +9164,13 @@
         <v>172.87</v>
       </c>
       <c r="H2" t="n">
-        <v>266.11</v>
+        <v>266.58</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>23.15</v>
+        <v>23.37</v>
       </c>
       <c r="K2" t="n">
         <v>27.65</v>
@@ -9188,7 +9188,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="Q2" t="n">
         <v>1.92</v>
@@ -9249,7 +9249,7 @@
         <v>5.88</v>
       </c>
       <c r="P3" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="Q3" t="n">
         <v>12.65</v>
@@ -9397,22 +9397,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.31</v>
+        <v>26.29</v>
       </c>
       <c r="D2" t="n">
-        <v>49.99</v>
+        <v>52.43</v>
       </c>
       <c r="G2" t="n">
-        <v>1318230000</v>
+        <v>1369270000</v>
       </c>
       <c r="H2" t="n">
-        <v>20.25</v>
+        <v>21.03</v>
       </c>
       <c r="I2" t="n">
         <v>45.6</v>
       </c>
       <c r="K2" t="n">
-        <v>80.17</v>
+        <v>73.45</v>
       </c>
       <c r="M2" t="n">
         <v>69.08</v>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="R2" t="n">
         <v>17.8</v>
@@ -9433,7 +9433,7 @@
         <v>1.33</v>
       </c>
       <c r="U2" t="n">
-        <v>71.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -9448,25 +9448,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>69.23999999999999</v>
+        <v>68.95</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50.41</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>14251550000</v>
+        <v>14191450000</v>
       </c>
       <c r="H3" t="n">
-        <v>55.39</v>
+        <v>55.16</v>
       </c>
       <c r="I3" t="n">
         <v>94.37</v>
       </c>
       <c r="K3" t="n">
-        <v>36.29</v>
+        <v>36.87</v>
       </c>
       <c r="L3" t="n">
         <v>38.99</v>
@@ -9481,19 +9481,19 @@
         <v>-20.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
         <v>26.66</v>
       </c>
       <c r="S3" t="n">
-        <v>57.43</v>
+        <v>57.42</v>
       </c>
       <c r="T3" t="n">
         <v>1.1</v>
       </c>
       <c r="U3" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="4">
@@ -9508,22 +9508,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58.82</v>
+        <v>60.62</v>
       </c>
       <c r="D4" t="n">
-        <v>45.46</v>
+        <v>47.86</v>
       </c>
       <c r="G4" t="n">
-        <v>10234150000</v>
+        <v>10547330000</v>
       </c>
       <c r="H4" t="n">
-        <v>47.06</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>50.05</v>
+        <v>45.6</v>
       </c>
       <c r="M4" t="n">
         <v>-173.38</v>
@@ -9532,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="R4" t="n">
         <v>16.16</v>
@@ -9544,7 +9544,7 @@
         <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>48.6</v>
+        <v>46.8</v>
       </c>
     </row>
   </sheetData>
@@ -9734,22 +9734,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45.23</v>
+        <v>45.28</v>
       </c>
       <c r="C3" t="n">
-        <v>50.34</v>
+        <v>50.66</v>
       </c>
       <c r="D3" t="n">
-        <v>18.77</v>
+        <v>18.79</v>
       </c>
       <c r="E3" t="n">
         <v>2.16</v>
       </c>
       <c r="F3" t="n">
-        <v>2237100000</v>
+        <v>2239570000</v>
       </c>
       <c r="G3" t="n">
-        <v>36.18</v>
+        <v>36.22</v>
       </c>
       <c r="H3" t="n">
         <v>59</v>
@@ -9758,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>30.44</v>
+        <v>30.3</v>
       </c>
       <c r="K3" t="n">
         <v>11.04</v>
@@ -9788,7 +9788,7 @@
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
     </row>
   </sheetData>
@@ -9914,22 +9914,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>204.65</v>
+        <v>206.96</v>
       </c>
       <c r="C2" t="n">
-        <v>45.34</v>
+        <v>47.38</v>
       </c>
       <c r="D2" t="n">
-        <v>31.34</v>
+        <v>31.69</v>
       </c>
       <c r="E2" t="n">
-        <v>19.54</v>
+        <v>19.76</v>
       </c>
       <c r="F2" t="n">
-        <v>4952529850000</v>
+        <v>5008311040000</v>
       </c>
       <c r="G2" t="n">
-        <v>163.72</v>
+        <v>165.57</v>
       </c>
       <c r="H2" t="n">
         <v>309.93</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>51.44</v>
+        <v>49.75</v>
       </c>
       <c r="K2" t="n">
         <v>85.23</v>
@@ -9956,19 +9956,19 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>4.09</v>
       </c>
       <c r="R2" t="n">
-        <v>69.2</v>
+        <v>69.19</v>
       </c>
       <c r="S2" t="n">
         <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>74.09999999999999</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -9978,22 +9978,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>512.48</v>
+        <v>531</v>
       </c>
       <c r="C3" t="n">
-        <v>57.68</v>
+        <v>60.35</v>
       </c>
       <c r="D3" t="n">
-        <v>168.2</v>
+        <v>174.28</v>
       </c>
       <c r="E3" t="n">
-        <v>22.31</v>
+        <v>23.12</v>
       </c>
       <c r="F3" t="n">
-        <v>835650160000</v>
+        <v>865848910000</v>
       </c>
       <c r="G3" t="n">
-        <v>409.98</v>
+        <v>424.8</v>
       </c>
       <c r="H3" t="n">
         <v>496.32</v>
@@ -10002,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.15</v>
+        <v>-6.53</v>
       </c>
       <c r="K3" t="n">
         <v>37.85</v>
@@ -10020,7 +10020,7 @@
         <v>0.06</v>
       </c>
       <c r="P3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
         <v>0.49</v>
@@ -10032,7 +10032,7 @@
         <v>1.49</v>
       </c>
       <c r="T3" t="n">
-        <v>49.8</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="4">
@@ -10042,22 +10042,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>392.9</v>
+        <v>403.89</v>
       </c>
       <c r="C4" t="n">
-        <v>46.15</v>
+        <v>49.36</v>
       </c>
       <c r="D4" t="n">
-        <v>65.41</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>24.77</v>
+        <v>25.46</v>
       </c>
       <c r="F4" t="n">
-        <v>1869253180000</v>
+        <v>1921539080000</v>
       </c>
       <c r="G4" t="n">
-        <v>314.32</v>
+        <v>323.11</v>
       </c>
       <c r="H4" t="n">
         <v>524.1799999999999</v>
@@ -10066,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>33.41</v>
+        <v>29.78</v>
       </c>
       <c r="K4" t="n">
         <v>47.87</v>
@@ -10090,13 +10090,13 @@
         <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>78.68000000000001</v>
+        <v>78.69</v>
       </c>
       <c r="S4" t="n">
         <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>60.2</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="5">
@@ -10106,31 +10106,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>289.54</v>
+        <v>307</v>
       </c>
       <c r="C5" t="n">
-        <v>61.16</v>
+        <v>64.02</v>
       </c>
       <c r="D5" t="n">
-        <v>98.94</v>
+        <v>104.91</v>
       </c>
       <c r="E5" t="n">
-        <v>29.06</v>
+        <v>30.81</v>
       </c>
       <c r="F5" t="n">
-        <v>253289590000</v>
+        <v>268563599999</v>
       </c>
       <c r="G5" t="n">
-        <v>231.63</v>
+        <v>245.6</v>
       </c>
       <c r="H5" t="n">
-        <v>244.35</v>
+        <v>247.55</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.61</v>
+        <v>-19.36</v>
       </c>
       <c r="K5" t="n">
         <v>27.57</v>
@@ -10148,19 +10148,19 @@
         <v>0.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
         <v>0.77</v>
       </c>
       <c r="R5" t="n">
-        <v>78.14</v>
+        <v>78.13</v>
       </c>
       <c r="S5" t="n">
         <v>1.43</v>
       </c>
       <c r="T5" t="n">
-        <v>37.7</v>
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -10286,22 +10286,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>267.17</v>
+        <v>269.96</v>
       </c>
       <c r="C2" t="n">
-        <v>47.79</v>
+        <v>49.44</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2</v>
+        <v>23.44</v>
       </c>
       <c r="E2" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="F2" t="n">
-        <v>96499160000</v>
+        <v>97505450000</v>
       </c>
       <c r="G2" t="n">
-        <v>213.74</v>
+        <v>215.97</v>
       </c>
       <c r="H2" t="n">
         <v>365.11</v>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>36.66</v>
+        <v>35.25</v>
       </c>
       <c r="K2" t="n">
         <v>23.45</v>
@@ -10334,13 +10334,13 @@
         <v>6.48</v>
       </c>
       <c r="R2" t="n">
-        <v>73.70999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="S2" t="n">
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>58.6</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="3">
@@ -10350,22 +10350,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>158.83</v>
+        <v>160.98</v>
       </c>
       <c r="C3" t="n">
-        <v>56.79</v>
+        <v>58.61</v>
       </c>
       <c r="D3" t="n">
-        <v>26.52</v>
+        <v>26.88</v>
       </c>
       <c r="E3" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>53554690000</v>
+        <v>54279630000</v>
       </c>
       <c r="G3" t="n">
-        <v>127.06</v>
+        <v>128.78</v>
       </c>
       <c r="H3" t="n">
         <v>230.29</v>
@@ -10374,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>44.99</v>
+        <v>43.06</v>
       </c>
       <c r="K3" t="n">
         <v>-10</v>
@@ -10404,7 +10404,7 @@
         <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="4">
@@ -10414,25 +10414,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>409.81</v>
+        <v>420</v>
       </c>
       <c r="C4" t="n">
-        <v>63.25</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.99</v>
+        <v>4.09</v>
       </c>
       <c r="F4" t="n">
-        <v>18603330000</v>
+        <v>19065910000</v>
       </c>
       <c r="G4" t="n">
-        <v>327.85</v>
+        <v>336</v>
       </c>
       <c r="H4" t="n">
         <v>478.62</v>
       </c>
       <c r="J4" t="n">
-        <v>16.79</v>
+        <v>13.96</v>
       </c>
       <c r="K4" t="n">
         <v>21.64</v>
@@ -10450,7 +10450,7 @@
         <v>6.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q4" t="n">
         <v>1.84</v>
@@ -10462,7 +10462,7 @@
         <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>51.9</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="5">
@@ -10472,22 +10472,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.82</v>
+        <v>60.62</v>
       </c>
       <c r="C5" t="n">
-        <v>45.46</v>
+        <v>47.86</v>
       </c>
       <c r="F5" t="n">
-        <v>10234150000</v>
+        <v>10547330000</v>
       </c>
       <c r="G5" t="n">
-        <v>47.06</v>
+        <v>48.5</v>
       </c>
       <c r="H5" t="n">
         <v>88.26000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>50.05</v>
+        <v>45.6</v>
       </c>
       <c r="L5" t="n">
         <v>-173.38</v>
@@ -10496,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Q5" t="n">
         <v>16.16</v>
@@ -10508,7 +10508,7 @@
         <v>1.95</v>
       </c>
       <c r="T5" t="n">
-        <v>48.6</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="6">
@@ -10518,25 +10518,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.34</v>
+        <v>10.62</v>
       </c>
       <c r="C6" t="n">
-        <v>45.27</v>
+        <v>47.12</v>
       </c>
       <c r="E6" t="n">
-        <v>202.41</v>
+        <v>207.87</v>
       </c>
       <c r="F6" t="n">
-        <v>3779080000</v>
+        <v>3880940000</v>
       </c>
       <c r="G6" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
         <v>15.64</v>
       </c>
       <c r="J6" t="n">
-        <v>51.26</v>
+        <v>47.27</v>
       </c>
       <c r="K6" t="n">
         <v>-95.78</v>
@@ -10554,7 +10554,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
         <v>3.08</v>
@@ -10566,7 +10566,7 @@
         <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="7">
@@ -10576,22 +10576,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.31</v>
+        <v>26.29</v>
       </c>
       <c r="C7" t="n">
-        <v>49.99</v>
+        <v>52.43</v>
       </c>
       <c r="F7" t="n">
-        <v>1318230000</v>
+        <v>1369270000</v>
       </c>
       <c r="G7" t="n">
-        <v>20.25</v>
+        <v>21.03</v>
       </c>
       <c r="H7" t="n">
         <v>45.6</v>
       </c>
       <c r="J7" t="n">
-        <v>80.17</v>
+        <v>73.45</v>
       </c>
       <c r="L7" t="n">
         <v>69.08</v>
@@ -10600,7 +10600,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="Q7" t="n">
         <v>17.8</v>
@@ -10612,7 +10612,7 @@
         <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>71.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10738,22 +10738,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>164.93</v>
+        <v>167.92</v>
       </c>
       <c r="C2" t="n">
-        <v>55.5</v>
+        <v>57.71</v>
       </c>
       <c r="D2" t="n">
-        <v>56.48</v>
+        <v>57.5</v>
       </c>
       <c r="E2" t="n">
-        <v>21.39</v>
+        <v>21.78</v>
       </c>
       <c r="F2" t="n">
-        <v>207680280000</v>
+        <v>211450970000</v>
       </c>
       <c r="G2" t="n">
-        <v>131.94</v>
+        <v>134.34</v>
       </c>
       <c r="H2" t="n">
         <v>190.3</v>
@@ -10762,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>15.38</v>
+        <v>13.33</v>
       </c>
       <c r="K2" t="n">
         <v>35.13</v>
@@ -10786,13 +10786,13 @@
         <v>17.07</v>
       </c>
       <c r="R2" t="n">
-        <v>72.05</v>
+        <v>72.02</v>
       </c>
       <c r="S2" t="n">
         <v>1.12</v>
       </c>
       <c r="T2" t="n">
-        <v>53.9</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="3">
@@ -10802,22 +10802,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>249.33</v>
+        <v>259.5</v>
       </c>
       <c r="C3" t="n">
-        <v>60.25</v>
+        <v>62.85</v>
       </c>
       <c r="D3" t="n">
-        <v>100.54</v>
+        <v>104.65</v>
       </c>
       <c r="E3" t="n">
-        <v>34.82</v>
+        <v>36.24</v>
       </c>
       <c r="F3" t="n">
-        <v>46494530000</v>
+        <v>48390990000</v>
       </c>
       <c r="G3" t="n">
-        <v>199.46</v>
+        <v>207.6</v>
       </c>
       <c r="H3" t="n">
         <v>266.44</v>
@@ -10826,7 +10826,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6.86</v>
+        <v>2.67</v>
       </c>
       <c r="K3" t="n">
         <v>157.02</v>
@@ -10844,19 +10844,19 @@
         <v>0.01</v>
       </c>
       <c r="P3" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="Q3" t="n">
         <v>10.3</v>
       </c>
       <c r="R3" t="n">
-        <v>75.22</v>
+        <v>75.39</v>
       </c>
       <c r="S3" t="n">
         <v>1.15</v>
       </c>
       <c r="T3" t="n">
-        <v>62.6</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="4">
@@ -10866,31 +10866,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374.68</v>
+        <v>385.6</v>
       </c>
       <c r="C4" t="n">
-        <v>63.89</v>
+        <v>65.64</v>
       </c>
       <c r="D4" t="n">
-        <v>252.55</v>
+        <v>259.91</v>
       </c>
       <c r="E4" t="n">
-        <v>64.13</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>64223130000</v>
+        <v>66094910000</v>
       </c>
       <c r="G4" t="n">
-        <v>299.74</v>
+        <v>308.48</v>
       </c>
       <c r="H4" t="n">
-        <v>253.06</v>
+        <v>257.11</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-32.46</v>
+        <v>-33.32</v>
       </c>
       <c r="K4" t="n">
         <v>93.40000000000001</v>
@@ -10908,19 +10908,19 @@
         <v>0.03</v>
       </c>
       <c r="P4" t="n">
-        <v>3.93</v>
+        <v>3.83</v>
       </c>
       <c r="Q4" t="n">
         <v>18.28</v>
       </c>
       <c r="R4" t="n">
-        <v>71.3</v>
+        <v>71.34</v>
       </c>
       <c r="S4" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="T4" t="n">
-        <v>56.7</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="5">
@@ -10930,22 +10930,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>378.85</v>
+        <v>390.6</v>
       </c>
       <c r="C5" t="n">
-        <v>51.15</v>
+        <v>53.54</v>
       </c>
       <c r="D5" t="n">
-        <v>180.87</v>
+        <v>186.48</v>
       </c>
       <c r="E5" t="n">
-        <v>11.23</v>
+        <v>11.57</v>
       </c>
       <c r="F5" t="n">
-        <v>74117960000</v>
+        <v>76416720000</v>
       </c>
       <c r="G5" t="n">
-        <v>303.08</v>
+        <v>312.48</v>
       </c>
       <c r="H5" t="n">
         <v>388.09</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44</v>
+        <v>-0.64</v>
       </c>
       <c r="K5" t="n">
         <v>20.55</v>
@@ -10972,19 +10972,19 @@
         <v>0.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
         <v>4.45</v>
       </c>
       <c r="R5" t="n">
-        <v>88.13</v>
+        <v>88.14</v>
       </c>
       <c r="S5" t="n">
         <v>1.65</v>
       </c>
       <c r="T5" t="n">
-        <v>50.7</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="6">
@@ -10994,22 +10994,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>869.98</v>
+        <v>885.98</v>
       </c>
       <c r="C6" t="n">
-        <v>47.35</v>
+        <v>48.76</v>
       </c>
       <c r="D6" t="n">
-        <v>161.46</v>
+        <v>164.43</v>
       </c>
       <c r="E6" t="n">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="F6" t="n">
-        <v>67684450000</v>
+        <v>68929370000</v>
       </c>
       <c r="G6" t="n">
-        <v>695.98</v>
+        <v>708.78</v>
       </c>
       <c r="H6" t="n">
         <v>1132.81</v>
@@ -11018,7 +11018,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>30.21</v>
+        <v>27.86</v>
       </c>
       <c r="K6" t="n">
         <v>90.12</v>
@@ -11042,13 +11042,13 @@
         <v>2.57</v>
       </c>
       <c r="R6" t="n">
-        <v>102.92</v>
+        <v>102.9</v>
       </c>
       <c r="S6" t="n">
         <v>1.48</v>
       </c>
       <c r="T6" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
     </row>
   </sheetData>
@@ -11174,31 +11174,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1043.19</v>
+        <v>1089.13</v>
       </c>
       <c r="C2" t="n">
-        <v>61.74</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>49.25</v>
+        <v>51.42</v>
       </c>
       <c r="E2" t="n">
-        <v>20.24</v>
+        <v>21.13</v>
       </c>
       <c r="F2" t="n">
-        <v>1176440780000</v>
+        <v>1228248940000</v>
       </c>
       <c r="G2" t="n">
-        <v>834.55</v>
+        <v>871.3</v>
       </c>
       <c r="H2" t="n">
-        <v>963.52</v>
+        <v>1002.27</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-7.64</v>
+        <v>-7.98</v>
       </c>
       <c r="K2" t="n">
         <v>196.29</v>
@@ -11216,7 +11216,7 @@
         <v>0.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
         <v>0.44</v>
@@ -11228,7 +11228,7 @@
         <v>1.35</v>
       </c>
       <c r="T2" t="n">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="3">
@@ -11238,22 +11238,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>712.13</v>
+        <v>754.89</v>
       </c>
       <c r="C3" t="n">
-        <v>75.73</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>42.51</v>
+        <v>45.06</v>
       </c>
       <c r="E3" t="n">
-        <v>20.84</v>
+        <v>22.09</v>
       </c>
       <c r="F3" t="n">
-        <v>245458490000</v>
+        <v>260197100000</v>
       </c>
       <c r="G3" t="n">
-        <v>569.7</v>
+        <v>603.91</v>
       </c>
       <c r="H3" t="n">
         <v>560</v>
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-21.36</v>
+        <v>-25.82</v>
       </c>
       <c r="K3" t="n">
         <v>45.47</v>
@@ -11280,19 +11280,19 @@
         <v>0.18</v>
       </c>
       <c r="P3" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
         <v>0.95</v>
       </c>
       <c r="R3" t="n">
-        <v>97.73999999999999</v>
+        <v>97.73</v>
       </c>
       <c r="S3" t="n">
         <v>1.72</v>
       </c>
       <c r="T3" t="n">
-        <v>52.1</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="4">
@@ -11302,22 +11302,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1066.07</v>
+        <v>1114.55</v>
       </c>
       <c r="C4" t="n">
-        <v>73.8</v>
+        <v>76.48</v>
       </c>
       <c r="D4" t="n">
-        <v>101.19</v>
+        <v>105.79</v>
       </c>
       <c r="E4" t="n">
-        <v>21.71</v>
+        <v>22.7</v>
       </c>
       <c r="F4" t="n">
-        <v>239043790000</v>
+        <v>249913860000</v>
       </c>
       <c r="G4" t="n">
-        <v>852.86</v>
+        <v>891.64</v>
       </c>
       <c r="H4" t="n">
         <v>903.55</v>
@@ -11326,7 +11326,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-15.24</v>
+        <v>-18.93</v>
       </c>
       <c r="K4" t="n">
         <v>44.07</v>
@@ -11344,7 +11344,7 @@
         <v>3.82</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
         <v>0.27</v>
@@ -11356,7 +11356,7 @@
         <v>1.59</v>
       </c>
       <c r="T4" t="n">
-        <v>43</v>
+        <v>41.9</v>
       </c>
     </row>
   </sheetData>
@@ -11482,22 +11482,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>187.08</v>
+        <v>189.12</v>
       </c>
       <c r="C2" t="n">
-        <v>48.63</v>
+        <v>51.42</v>
       </c>
       <c r="D2" t="n">
-        <v>49.48</v>
+        <v>50.02</v>
       </c>
       <c r="E2" t="n">
-        <v>10.24</v>
+        <v>10.36</v>
       </c>
       <c r="F2" t="n">
-        <v>65741039999</v>
+        <v>66457920000</v>
       </c>
       <c r="G2" t="n">
-        <v>149.66</v>
+        <v>151.3</v>
       </c>
       <c r="H2" t="n">
         <v>219.17</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>17.15</v>
+        <v>15.89</v>
       </c>
       <c r="K2" t="n">
         <v>16.16</v>
@@ -11536,7 +11536,7 @@
         <v>1.61</v>
       </c>
       <c r="T2" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="3">
@@ -11546,22 +11546,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1088.52</v>
+        <v>1094</v>
       </c>
       <c r="C3" t="n">
-        <v>57.24</v>
+        <v>58.81</v>
       </c>
       <c r="D3" t="n">
-        <v>75.28</v>
+        <v>75.66</v>
       </c>
       <c r="E3" t="n">
-        <v>11.38</v>
+        <v>11.43</v>
       </c>
       <c r="F3" t="n">
-        <v>107354470000</v>
+        <v>107894930000</v>
       </c>
       <c r="G3" t="n">
-        <v>870.8200000000001</v>
+        <v>875.2</v>
       </c>
       <c r="H3" t="n">
         <v>1204.61</v>
@@ -11570,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10.66</v>
+        <v>10.11</v>
       </c>
       <c r="K3" t="n">
         <v>9.84</v>
@@ -11600,7 +11600,7 @@
         <v>1.48</v>
       </c>
       <c r="T3" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="4">
@@ -11610,25 +11610,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.57</v>
+        <v>47.15</v>
       </c>
       <c r="C4" t="n">
-        <v>55.55</v>
+        <v>58.11</v>
       </c>
       <c r="E4" t="n">
-        <v>36.64</v>
+        <v>37.91</v>
       </c>
       <c r="F4" t="n">
-        <v>13022520000</v>
+        <v>13474040000</v>
       </c>
       <c r="G4" t="n">
-        <v>36.46</v>
+        <v>37.72</v>
       </c>
       <c r="H4" t="n">
         <v>72.92</v>
       </c>
       <c r="J4" t="n">
-        <v>60.02</v>
+        <v>54.66</v>
       </c>
       <c r="K4" t="n">
         <v>139.29</v>
@@ -11646,19 +11646,19 @@
         <v>1.72</v>
       </c>
       <c r="P4" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="Q4" t="n">
         <v>9.48</v>
       </c>
       <c r="R4" t="n">
-        <v>70.27</v>
+        <v>70.28</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>43.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="5">
@@ -11668,28 +11668,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125.44</v>
+        <v>126.99</v>
       </c>
       <c r="C5" t="n">
-        <v>50.25</v>
+        <v>53.05</v>
       </c>
       <c r="D5" t="n">
-        <v>137.74</v>
+        <v>139.44</v>
       </c>
       <c r="E5" t="n">
-        <v>5.15</v>
+        <v>5.21</v>
       </c>
       <c r="F5" t="n">
-        <v>37321500000</v>
+        <v>37782660000</v>
       </c>
       <c r="G5" t="n">
-        <v>100.35</v>
+        <v>101.59</v>
       </c>
       <c r="H5" t="n">
         <v>131.55</v>
       </c>
       <c r="J5" t="n">
-        <v>4.87</v>
+        <v>3.59</v>
       </c>
       <c r="K5" t="n">
         <v>21.58</v>
@@ -11716,7 +11716,7 @@
         <v>1.5</v>
       </c>
       <c r="T5" t="n">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
     </row>
   </sheetData>
@@ -11842,22 +11842,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>317.58</v>
+        <v>328.98</v>
       </c>
       <c r="C2" t="n">
-        <v>51.37</v>
+        <v>55.37</v>
       </c>
       <c r="D2" t="n">
-        <v>79.72</v>
+        <v>82.59</v>
       </c>
       <c r="E2" t="n">
-        <v>11.25</v>
+        <v>11.65</v>
       </c>
       <c r="F2" t="n">
-        <v>121985280000</v>
+        <v>126364130000</v>
       </c>
       <c r="G2" t="n">
-        <v>254.06</v>
+        <v>263.18</v>
       </c>
       <c r="H2" t="n">
         <v>380.63</v>
@@ -11866,7 +11866,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19.85</v>
+        <v>15.7</v>
       </c>
       <c r="K2" t="n">
         <v>30.13</v>
@@ -11884,19 +11884,19 @@
         <v>0.77</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
         <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>84.73</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>1.58</v>
       </c>
       <c r="T2" t="n">
-        <v>53.7</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="3">
@@ -11906,22 +11906,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>283.88</v>
+        <v>288.5</v>
       </c>
       <c r="C3" t="n">
-        <v>53.87</v>
+        <v>55.59</v>
       </c>
       <c r="D3" t="n">
-        <v>126.82</v>
+        <v>128.89</v>
       </c>
       <c r="E3" t="n">
-        <v>4.71</v>
+        <v>4.79</v>
       </c>
       <c r="F3" t="n">
-        <v>14993340000</v>
+        <v>15237360000</v>
       </c>
       <c r="G3" t="n">
-        <v>227.1</v>
+        <v>230.8</v>
       </c>
       <c r="H3" t="n">
         <v>351.75</v>
@@ -11930,7 +11930,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>23.91</v>
+        <v>21.92</v>
       </c>
       <c r="K3" t="n">
         <v>47.47</v>
@@ -11960,7 +11960,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="4">
@@ -11970,22 +11970,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>133.36</v>
+        <v>134.7</v>
       </c>
       <c r="C4" t="n">
-        <v>54.18</v>
+        <v>55.35</v>
       </c>
       <c r="D4" t="n">
-        <v>93.81</v>
+        <v>94.75</v>
       </c>
       <c r="E4" t="n">
-        <v>6.76</v>
+        <v>6.82</v>
       </c>
       <c r="F4" t="n">
-        <v>10923740000</v>
+        <v>11033510000</v>
       </c>
       <c r="G4" t="n">
-        <v>106.69</v>
+        <v>107.76</v>
       </c>
       <c r="H4" t="n">
         <v>149.75</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>12.29</v>
+        <v>11.17</v>
       </c>
       <c r="K4" t="n">
         <v>54.3</v>
@@ -12012,7 +12012,7 @@
         <v>0.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Q4" t="n">
         <v>16.68</v>
@@ -12024,7 +12024,7 @@
         <v>1.67</v>
       </c>
       <c r="T4" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
     </row>
   </sheetData>
@@ -12150,22 +12150,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>714.85</v>
+        <v>725</v>
       </c>
       <c r="C2" t="n">
-        <v>52.65</v>
+        <v>54.99</v>
       </c>
       <c r="D2" t="n">
-        <v>98.06999999999999</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="F2" t="n">
-        <v>107270490000</v>
+        <v>108793600000</v>
       </c>
       <c r="G2" t="n">
-        <v>571.88</v>
+        <v>580</v>
       </c>
       <c r="H2" t="n">
         <v>802.79</v>
@@ -12174,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12.3</v>
+        <v>10.73</v>
       </c>
       <c r="K2" t="n">
         <v>26.33</v>
@@ -12192,19 +12192,19 @@
         <v>0.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>93.23999999999999</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>1.69</v>
       </c>
       <c r="T2" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="3">
@@ -12214,22 +12214,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1048.86</v>
+        <v>1073</v>
       </c>
       <c r="C3" t="n">
-        <v>59.46</v>
+        <v>62.1</v>
       </c>
       <c r="D3" t="n">
-        <v>30.56</v>
+        <v>31.26</v>
       </c>
       <c r="E3" t="n">
-        <v>7.16</v>
+        <v>7.33</v>
       </c>
       <c r="F3" t="n">
-        <v>281849660000</v>
+        <v>288336560000</v>
       </c>
       <c r="G3" t="n">
-        <v>839.09</v>
+        <v>858.4</v>
       </c>
       <c r="H3" t="n">
         <v>1227.4</v>
@@ -12238,7 +12238,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>17.02</v>
+        <v>14.39</v>
       </c>
       <c r="K3" t="n">
         <v>15.98</v>
@@ -12256,19 +12256,19 @@
         <v>0.21</v>
       </c>
       <c r="P3" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
         <v>0.15</v>
       </c>
       <c r="R3" t="n">
-        <v>78.51000000000001</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>1.69</v>
       </c>
       <c r="T3" t="n">
-        <v>54.7</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="4">
@@ -12278,22 +12278,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170.94</v>
+        <v>174.5</v>
       </c>
       <c r="C4" t="n">
-        <v>57.62</v>
+        <v>60.69</v>
       </c>
       <c r="D4" t="n">
-        <v>57.49</v>
+        <v>58.68</v>
       </c>
       <c r="E4" t="n">
-        <v>6.39</v>
+        <v>6.52</v>
       </c>
       <c r="F4" t="n">
-        <v>27644490000</v>
+        <v>28220220000</v>
       </c>
       <c r="G4" t="n">
-        <v>136.75</v>
+        <v>139.6</v>
       </c>
       <c r="H4" t="n">
         <v>194.67</v>
@@ -12302,7 +12302,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>13.88</v>
+        <v>11.56</v>
       </c>
       <c r="K4" t="n">
         <v>53.47</v>
@@ -12320,19 +12320,19 @@
         <v>0.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q4" t="n">
         <v>0.99</v>
       </c>
       <c r="R4" t="n">
-        <v>93.70999999999999</v>
+        <v>93.66</v>
       </c>
       <c r="S4" t="n">
         <v>1.53</v>
       </c>
       <c r="T4" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="5">
@@ -12342,22 +12342,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>294.03</v>
+        <v>300.5</v>
       </c>
       <c r="C5" t="n">
-        <v>53.82</v>
+        <v>56.18</v>
       </c>
       <c r="D5" t="n">
-        <v>57.46</v>
+        <v>58.73</v>
       </c>
       <c r="E5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="F5" t="n">
-        <v>10711990000</v>
+        <v>10947710000</v>
       </c>
       <c r="G5" t="n">
-        <v>235.22</v>
+        <v>240.4</v>
       </c>
       <c r="H5" t="n">
         <v>289.17</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.65</v>
+        <v>-3.77</v>
       </c>
       <c r="K5" t="n">
         <v>6.45</v>
@@ -12390,13 +12390,13 @@
         <v>21.68</v>
       </c>
       <c r="R5" t="n">
-        <v>81.45999999999999</v>
+        <v>80.48</v>
       </c>
       <c r="S5" t="n">
         <v>1.86</v>
       </c>
       <c r="T5" t="n">
-        <v>43.3</v>
+        <v>42.5</v>
       </c>
     </row>
   </sheetData>
@@ -12522,22 +12522,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>409.64</v>
+        <v>419.79</v>
       </c>
       <c r="C2" t="n">
-        <v>53.88</v>
+        <v>57.76</v>
       </c>
       <c r="D2" t="n">
-        <v>40.05</v>
+        <v>41.04</v>
       </c>
       <c r="E2" t="n">
-        <v>5.58</v>
+        <v>5.72</v>
       </c>
       <c r="F2" t="n">
-        <v>159063210000</v>
+        <v>163004450000</v>
       </c>
       <c r="G2" t="n">
-        <v>327.71</v>
+        <v>335.83</v>
       </c>
       <c r="H2" t="n">
         <v>463.71</v>
@@ -12546,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>13.2</v>
+        <v>10.46</v>
       </c>
       <c r="K2" t="n">
         <v>16.84</v>
@@ -12564,7 +12564,7 @@
         <v>1.11</v>
       </c>
       <c r="P2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Q2" t="n">
         <v>0.2</v>
@@ -12576,7 +12576,7 @@
         <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
     </row>
   </sheetData>
